--- a/Ancestors Database_v2.xlsx
+++ b/Ancestors Database_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\North_American_Management_Work\compare_book_of_negroes_records\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10112F60-9690-4EC1-9C37-214896AEFF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70D654C-9323-4CA6-8CBD-C66029604F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46110" yWindow="0" windowWidth="26085" windowHeight="20985" xr2:uid="{0C8A6B89-EB97-4AFD-AB2D-26665E6E306C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0C8A6B89-EB97-4AFD-AB2D-26665E6E306C}"/>
   </bookViews>
   <sheets>
     <sheet name="Brooker" sheetId="1" r:id="rId1"/>
@@ -896,7 +896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1071,7 +1071,7 @@
     <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1081,7 +1081,7 @@
     <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1091,7 +1091,7 @@
     <xf numFmtId="164" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1101,7 +1101,7 @@
     <xf numFmtId="164" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1111,15 +1111,14 @@
     <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1132,8 +1131,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1480,474 +1477,461 @@
   <dimension ref="A1:QY30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="80"/>
-    <col min="14" max="14" width="21.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="29" style="80" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="40.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="27.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="24.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="28.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="24.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="29.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="27.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="28.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="24.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="17.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="29.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="22.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="40.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="24.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="30.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="41.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="9.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="30.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="24.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="30.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="24.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="29.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="27.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="14.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="28.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="24.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="10.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="19.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="11.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="9.140625" style="80"/>
-    <col min="92" max="92" width="29.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="40.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="30.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="41.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="9.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="30.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="109" max="109" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="110" max="110" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="111" max="111" width="30.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="112" max="112" width="24.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="114" max="114" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="115" max="115" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="116" max="116" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="118" max="118" width="29.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="119" max="119" width="27.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="120" max="120" width="14.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="121" max="121" width="28.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="122" max="122" width="24.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="123" max="123" width="10.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="124" max="124" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="127" max="127" width="19.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="128" max="128" width="11.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="129" max="129" width="9.140625" style="80"/>
-    <col min="130" max="130" width="29.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="131" max="131" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="132" max="132" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="134" max="134" width="40.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="135" max="135" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="136" max="136" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="138" max="138" width="30.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="139" max="139" width="41.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="140" max="140" width="30.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="141" max="141" width="9.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="143" max="143" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="144" max="144" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="145" max="145" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="146" max="146" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="147" max="147" width="30.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="148" max="148" width="24.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="149" max="149" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="150" max="150" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="151" max="151" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="152" max="152" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="153" max="153" width="29.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="154" max="154" width="27.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="155" max="155" width="7.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="156" max="156" width="28.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="157" max="157" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="158" max="158" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="159" max="159" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="160" max="160" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="161" max="161" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="162" max="162" width="19.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="163" max="163" width="11.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="164" max="164" width="9.140625" style="80"/>
-    <col min="165" max="165" width="29.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="166" max="166" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="167" max="167" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="168" max="168" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="169" max="169" width="40.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="170" max="170" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="171" max="171" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="172" max="172" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="173" max="173" width="30.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="174" max="174" width="41.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="175" max="175" width="9.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="176" max="176" width="30.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="177" max="177" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="178" max="178" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="179" max="179" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="180" max="180" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="181" max="181" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="182" max="182" width="30.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="183" max="183" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="184" max="184" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="185" max="185" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="186" max="186" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="187" max="187" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="188" max="188" width="29.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="189" max="189" width="27.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="190" max="190" width="7.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="191" max="191" width="28.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="192" max="192" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="193" max="193" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="194" max="194" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="195" max="195" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="196" max="196" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="197" max="197" width="19.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="198" max="198" width="11.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="199" max="199" width="9.140625" style="80"/>
-    <col min="200" max="200" width="29.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="201" max="201" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="202" max="202" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="203" max="203" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="204" max="204" width="40.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="205" max="205" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="206" max="206" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="207" max="207" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="208" max="208" width="30.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="209" max="209" width="41.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="210" max="210" width="9.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="211" max="211" width="30.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="212" max="212" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="213" max="213" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="214" max="214" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="215" max="215" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="216" max="216" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="217" max="217" width="30.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="218" max="218" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="219" max="219" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="220" max="220" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="221" max="221" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="222" max="222" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="223" max="223" width="29.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="224" max="224" width="27.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="225" max="225" width="7.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="226" max="226" width="28.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="227" max="227" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="228" max="228" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="229" max="229" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="230" max="230" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="231" max="231" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="232" max="232" width="19.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="233" max="233" width="11.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="234" max="234" width="9.140625" style="80"/>
-    <col min="235" max="235" width="29.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="236" max="236" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="237" max="237" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="238" max="238" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="239" max="239" width="40.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="240" max="240" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="241" max="241" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="242" max="242" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="243" max="243" width="30.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="244" max="244" width="41.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="245" max="245" width="9.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="246" max="246" width="30.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="247" max="247" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="248" max="248" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="249" max="249" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="250" max="250" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="251" max="251" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="252" max="252" width="30.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="253" max="253" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="254" max="254" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="255" max="255" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="256" max="256" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="257" max="257" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="258" max="258" width="29.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="259" max="259" width="27.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="260" max="260" width="7.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="261" max="261" width="28.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="262" max="262" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="263" max="263" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="264" max="264" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="265" max="265" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="266" max="266" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="267" max="267" width="19.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="268" max="268" width="11.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="269" max="269" width="9.140625" style="80"/>
-    <col min="270" max="270" width="29.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="271" max="271" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="272" max="272" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="273" max="273" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="274" max="274" width="40.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="275" max="275" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="276" max="276" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="277" max="277" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="278" max="278" width="30.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="279" max="279" width="41.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="280" max="280" width="9.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="281" max="281" width="30.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="282" max="282" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="283" max="283" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="284" max="284" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="285" max="285" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="286" max="286" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="287" max="287" width="30.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="288" max="288" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="289" max="289" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="290" max="290" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="291" max="291" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="292" max="292" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="293" max="293" width="29.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="294" max="294" width="27.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="295" max="295" width="7.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="296" max="296" width="28.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="297" max="297" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="298" max="298" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="299" max="299" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="300" max="300" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="301" max="301" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="302" max="302" width="19.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="303" max="303" width="11.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="304" max="304" width="9.140625" style="80"/>
-    <col min="305" max="305" width="29.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="306" max="306" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="307" max="307" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="308" max="308" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="309" max="309" width="40.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="310" max="310" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="311" max="311" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="312" max="312" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="313" max="313" width="30.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="314" max="314" width="41.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="315" max="315" width="9.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="316" max="316" width="30.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="317" max="317" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="318" max="318" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="319" max="319" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="320" max="320" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="321" max="321" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="322" max="322" width="30.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="323" max="323" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="324" max="324" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="325" max="325" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="326" max="326" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="327" max="327" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="328" max="328" width="29.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="329" max="329" width="27.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="330" max="330" width="7.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="331" max="331" width="28.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="332" max="332" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="333" max="333" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="334" max="334" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="335" max="335" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="336" max="336" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="337" max="337" width="19.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="338" max="338" width="11.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="339" max="339" width="9.140625" style="80"/>
-    <col min="340" max="340" width="29.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="341" max="341" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="342" max="342" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="343" max="343" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="344" max="344" width="40.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="345" max="345" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="346" max="346" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="347" max="347" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="348" max="348" width="30.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="349" max="349" width="41.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="350" max="350" width="9.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="351" max="351" width="30.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="352" max="352" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="353" max="353" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="354" max="354" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="355" max="355" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="356" max="356" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="357" max="357" width="30.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="358" max="358" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="359" max="359" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="360" max="360" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="361" max="361" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="362" max="362" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="363" max="363" width="29.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="364" max="364" width="27.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="365" max="365" width="7.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="366" max="366" width="28.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="367" max="367" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="368" max="368" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="369" max="369" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="370" max="370" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="371" max="371" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="372" max="372" width="19.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="373" max="373" width="11.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="374" max="374" width="9.140625" style="80"/>
-    <col min="375" max="375" width="29.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="376" max="376" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="377" max="377" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="378" max="378" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="379" max="379" width="40.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="380" max="380" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="381" max="381" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="382" max="382" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="383" max="383" width="30.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="384" max="384" width="41.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="385" max="385" width="9.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="386" max="386" width="30.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="387" max="387" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="388" max="388" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="389" max="389" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="390" max="390" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="391" max="391" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="392" max="392" width="30.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="393" max="393" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="394" max="394" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="395" max="395" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="396" max="396" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="397" max="397" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="398" max="398" width="29.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="399" max="399" width="27.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="400" max="400" width="7.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="401" max="401" width="28.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="402" max="402" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="403" max="403" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="404" max="404" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="405" max="405" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="406" max="406" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="407" max="407" width="19.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="408" max="408" width="11.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="409" max="409" width="9.140625" style="80"/>
-    <col min="410" max="410" width="29.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="411" max="411" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="412" max="412" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="413" max="413" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="414" max="414" width="40.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="415" max="415" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="416" max="416" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="417" max="417" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="418" max="418" width="30.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="419" max="419" width="41.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="420" max="420" width="9.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="421" max="421" width="30.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="422" max="422" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="423" max="423" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="424" max="424" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="425" max="425" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="426" max="426" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="427" max="427" width="30.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="428" max="428" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="429" max="429" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="430" max="430" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="431" max="431" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="432" max="432" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="433" max="433" width="29.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="434" max="434" width="27.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="435" max="435" width="7.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="436" max="436" width="28.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="437" max="437" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="438" max="438" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="439" max="439" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="440" max="440" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="441" max="441" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="442" max="442" width="19.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="443" max="443" width="11.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="444" max="444" width="9.140625" style="80"/>
-    <col min="445" max="445" width="29.5703125" style="80" bestFit="1" customWidth="1"/>
-    <col min="446" max="446" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="447" max="447" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="448" max="448" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="449" max="449" width="40.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="450" max="450" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="451" max="451" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="452" max="452" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="453" max="453" width="30.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="454" max="454" width="41.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="455" max="455" width="9.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="456" max="456" width="30.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="457" max="457" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="458" max="458" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="459" max="459" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="460" max="460" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="461" max="461" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="462" max="462" width="30.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="463" max="463" width="22.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="464" max="464" width="10.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="465" max="465" width="11.85546875" style="80" bestFit="1" customWidth="1"/>
-    <col min="466" max="466" width="9.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="467" max="467" width="13.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="468" max="16384" width="9.140625" style="80"/>
+    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="29" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="123" max="123" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="132" max="132" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="134" max="134" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="135" max="135" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="136" max="136" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="138" max="138" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="140" max="140" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="143" max="143" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="144" max="144" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="145" max="145" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="146" max="146" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="147" max="147" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="148" max="148" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="149" max="149" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="150" max="150" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="151" max="151" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="152" max="152" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="153" max="153" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="154" max="154" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="155" max="155" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="156" max="156" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="157" max="157" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="158" max="158" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="159" max="159" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="160" max="160" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="161" max="161" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="162" max="162" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="163" max="163" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="165" max="165" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="166" max="166" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="167" max="167" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="168" max="168" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="169" max="169" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="170" max="170" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="171" max="171" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="172" max="172" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="173" max="173" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="174" max="174" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="175" max="175" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="176" max="176" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="177" max="177" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="178" max="178" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="179" max="179" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="180" max="180" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="181" max="181" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="182" max="182" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="183" max="183" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="184" max="184" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="185" max="185" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="186" max="186" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="187" max="187" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="188" max="188" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="189" max="189" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="190" max="190" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="191" max="191" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="192" max="192" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="193" max="193" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="194" max="194" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="195" max="195" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="196" max="196" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="197" max="197" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="198" max="198" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="200" max="200" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="201" max="201" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="202" max="202" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="203" max="203" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="204" max="204" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="205" max="205" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="206" max="206" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="207" max="207" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="208" max="208" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="209" max="209" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="210" max="210" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="211" max="211" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="212" max="212" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="213" max="213" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="214" max="214" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="215" max="215" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="216" max="216" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="217" max="217" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="218" max="218" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="219" max="219" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="220" max="220" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="221" max="221" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="222" max="222" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="223" max="223" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="224" max="224" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="225" max="225" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="226" max="226" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="227" max="227" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="228" max="228" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="229" max="229" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="230" max="230" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="231" max="231" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="232" max="232" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="233" max="233" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="235" max="235" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="236" max="236" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="237" max="237" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="238" max="238" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="239" max="239" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="240" max="240" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="241" max="241" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="242" max="242" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="243" max="243" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="244" max="244" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="245" max="245" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="246" max="246" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="247" max="247" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="248" max="248" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="249" max="249" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="250" max="250" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="251" max="251" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="252" max="252" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="253" max="253" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="254" max="254" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="255" max="255" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="256" max="256" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="257" max="257" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="258" max="258" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="259" max="259" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="260" max="260" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="261" max="261" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="262" max="262" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="263" max="263" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="264" max="264" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="265" max="265" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="266" max="266" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="267" max="267" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="268" max="268" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="270" max="270" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="271" max="271" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="272" max="272" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="273" max="273" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="274" max="274" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="275" max="275" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="276" max="276" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="277" max="277" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="278" max="278" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="279" max="279" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="280" max="280" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="281" max="281" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="282" max="282" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="283" max="283" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="284" max="284" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="285" max="285" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="286" max="286" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="287" max="287" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="288" max="288" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="289" max="289" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="290" max="290" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="291" max="291" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="292" max="292" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="293" max="293" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="294" max="294" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="295" max="295" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="296" max="296" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="297" max="297" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="298" max="298" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="299" max="299" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="300" max="300" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="301" max="301" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="302" max="302" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="303" max="303" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="305" max="305" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="306" max="306" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="307" max="307" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="308" max="308" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="309" max="309" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="310" max="310" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="311" max="311" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="312" max="312" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="313" max="313" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="314" max="314" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="315" max="315" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="316" max="316" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="317" max="317" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="318" max="318" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="319" max="319" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="320" max="320" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="321" max="321" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="322" max="322" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="323" max="323" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="324" max="324" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="325" max="325" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="326" max="326" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="327" max="327" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="328" max="328" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="329" max="329" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="330" max="330" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="331" max="331" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="332" max="332" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="333" max="333" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="334" max="334" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="335" max="335" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="336" max="336" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="337" max="337" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="338" max="338" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="340" max="340" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="341" max="341" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="342" max="342" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="343" max="343" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="344" max="344" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="345" max="345" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="346" max="346" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="347" max="347" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="348" max="348" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="349" max="349" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="350" max="350" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="351" max="351" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="352" max="352" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="353" max="353" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="354" max="354" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="355" max="355" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="356" max="356" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="357" max="357" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="358" max="358" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="359" max="359" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="360" max="360" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="361" max="361" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="362" max="362" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="363" max="363" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="364" max="364" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="365" max="365" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="366" max="366" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="367" max="367" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="368" max="368" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="369" max="369" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="370" max="370" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="371" max="371" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="372" max="372" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="373" max="373" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="375" max="375" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="376" max="376" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="377" max="377" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="378" max="378" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="379" max="379" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="380" max="380" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="381" max="381" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="382" max="382" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="383" max="383" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="384" max="384" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="385" max="385" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="386" max="386" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="387" max="387" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="388" max="388" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="389" max="389" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="390" max="390" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="391" max="391" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="392" max="392" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="393" max="393" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="394" max="394" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="395" max="395" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="396" max="396" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="397" max="397" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="398" max="398" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="399" max="399" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="400" max="400" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="401" max="401" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="402" max="402" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="403" max="403" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="404" max="404" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="405" max="405" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="406" max="406" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="407" max="407" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="408" max="408" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="410" max="410" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="411" max="411" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="412" max="412" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="413" max="413" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="414" max="414" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="415" max="415" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="416" max="416" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="417" max="417" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="418" max="418" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="419" max="419" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="420" max="420" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="421" max="421" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="422" max="422" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="423" max="423" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="424" max="424" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="425" max="425" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="426" max="426" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="427" max="427" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="428" max="428" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="429" max="429" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="430" max="430" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="431" max="431" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="432" max="432" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="433" max="433" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="434" max="434" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="435" max="435" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="436" max="436" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="437" max="437" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="438" max="438" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="439" max="439" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="440" max="440" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="441" max="441" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="442" max="442" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="443" max="443" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="445" max="445" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="446" max="446" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="447" max="447" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="448" max="448" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="449" max="449" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="450" max="450" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="451" max="451" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="452" max="452" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="453" max="453" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="454" max="454" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="455" max="455" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="456" max="456" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="457" max="457" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="458" max="458" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="459" max="459" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="460" max="460" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="461" max="461" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="462" max="462" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="463" max="463" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="464" max="464" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="465" max="465" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="466" max="466" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="467" max="467" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:467" s="79" customFormat="1" x14ac:dyDescent="0.25">
@@ -3354,5291 +3338,5291 @@
       </c>
     </row>
     <row r="2" spans="1:467" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="81">
+      <c r="D2" s="80">
         <v>1765</v>
       </c>
-      <c r="E2" s="81" t="s">
+      <c r="E2" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="81" t="s">
+      <c r="F2" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="G2" s="81" t="s">
+      <c r="G2" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="H2" s="81"/>
-      <c r="I2" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="81" t="s">
+      <c r="H2" s="80"/>
+      <c r="I2" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="L2" s="81" t="s">
+      <c r="L2" s="80" t="s">
         <v>141</v>
       </c>
-      <c r="M2" s="80" t="s">
+      <c r="M2" t="s">
         <v>140</v>
       </c>
-      <c r="N2" s="81" t="s">
+      <c r="N2" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="O2" s="81" t="s">
+      <c r="O2" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="P2" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81" t="s">
+      <c r="P2" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="81" t="s">
+      <c r="T2" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="U2" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="W2" s="81"/>
-      <c r="X2" s="81" t="s">
+      <c r="U2" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="Y2" s="81" t="s">
+      <c r="Y2" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="Z2" s="81"/>
-      <c r="AA2" s="81" t="s">
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="AB2" s="81" t="s">
+      <c r="AB2" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="AC2" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD2" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE2" s="81"/>
-      <c r="AF2" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG2" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AH2" s="81" t="s">
+      <c r="AC2" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD2" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE2" s="80"/>
+      <c r="AF2" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG2" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH2" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="AI2" s="81" t="s">
+      <c r="AI2" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AJ2" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AK2" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AL2" s="82"/>
-      <c r="AW2" s="80" t="s">
+      <c r="AJ2" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK2" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL2" s="81"/>
+      <c r="AW2" t="s">
         <v>136</v>
       </c>
-      <c r="AX2" s="80" t="s">
+      <c r="AX2" t="s">
         <v>141</v>
       </c>
-      <c r="AY2" s="80" t="s">
+      <c r="AY2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:467" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="83">
-        <v>2</v>
-      </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="W3" s="83"/>
-      <c r="X3" s="83"/>
-      <c r="Y3" s="83"/>
-      <c r="Z3" s="83"/>
+    <row r="3" spans="1:467" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="82">
+        <v>2</v>
+      </c>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="82"/>
     </row>
     <row r="4" spans="1:467" x14ac:dyDescent="0.25">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="81" t="s">
+      <c r="C4" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="81">
+      <c r="D4" s="80">
         <v>1790</v>
       </c>
-      <c r="E4" s="81" t="s">
+      <c r="E4" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="81" t="s">
+      <c r="F4" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="81"/>
-      <c r="I4" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="81" t="s">
+      <c r="H4" s="80"/>
+      <c r="I4" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="O4" s="81" t="s">
+      <c r="O4" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q4" s="81" t="s">
+      <c r="P4" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="R4" s="81"/>
-      <c r="S4" s="81"/>
-      <c r="T4" s="81" t="s">
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="U4" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="V4" s="81" t="s">
+      <c r="U4" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="W4" s="81"/>
-      <c r="X4" s="81" t="s">
+      <c r="W4" s="80"/>
+      <c r="X4" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="Y4" s="81" t="s">
+      <c r="Y4" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="86" t="s">
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="AB4" s="80" t="s">
+      <c r="AB4" t="s">
         <v>135</v>
       </c>
-      <c r="AC4" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD4" s="81" t="s">
+      <c r="AC4" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD4" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="AE4" s="81"/>
-      <c r="AF4" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG4" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM4" s="81" t="s">
+      <c r="AE4" s="80"/>
+      <c r="AF4" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG4" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM4" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="AN4" s="81" t="s">
+      <c r="AN4" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="AO4" s="81" t="s">
+      <c r="AO4" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="AP4" s="81">
+      <c r="AP4" s="80">
         <v>1765</v>
       </c>
-      <c r="AQ4" s="81" t="s">
+      <c r="AQ4" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="AR4" s="81" t="s">
+      <c r="AR4" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="AS4" s="81" t="s">
+      <c r="AS4" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="AT4" s="81"/>
-      <c r="AU4" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV4" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AW4" s="81" t="s">
+      <c r="AT4" s="80"/>
+      <c r="AU4" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV4" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW4" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="AZ4" s="81" t="s">
+      <c r="AZ4" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="BA4" s="81" t="s">
+      <c r="BA4" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="BB4" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC4" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD4" s="81"/>
-      <c r="BE4" s="81" t="s">
+      <c r="BB4" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC4" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD4" s="80"/>
+      <c r="BE4" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="BF4" s="81" t="s">
+      <c r="BF4" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="BG4" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BH4" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BI4" s="81"/>
-      <c r="BJ4" s="81" t="s">
+      <c r="BG4" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH4" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BI4" s="80"/>
+      <c r="BJ4" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="BK4" s="81" t="s">
+      <c r="BK4" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="BL4" s="81"/>
-      <c r="BM4" s="81" t="s">
+      <c r="BL4" s="80"/>
+      <c r="BM4" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="BN4" s="81" t="s">
+      <c r="BN4" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="BO4" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BP4" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BQ4" s="81"/>
-      <c r="BR4" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="BS4" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="BT4" s="81" t="s">
+      <c r="BO4" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP4" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BQ4" s="80"/>
+      <c r="BR4" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS4" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="BT4" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="BU4" s="81" t="s">
+      <c r="BU4" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="BV4" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="BW4" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="BX4" s="82"/>
-      <c r="BY4" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="BZ4" s="82" t="s">
+      <c r="BV4" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW4" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="BX4" s="81"/>
+      <c r="BY4" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="BZ4" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:467" x14ac:dyDescent="0.25">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="81" t="s">
+      <c r="C5" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="81" t="s">
+      <c r="E5" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="81" t="s">
+      <c r="F5" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="H5" s="81"/>
-      <c r="I5" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="81" t="s">
+      <c r="H5" s="80"/>
+      <c r="I5" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="81" t="s">
+      <c r="O5" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="P5" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q5" s="81" t="s">
+      <c r="P5" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="R5" s="81"/>
-      <c r="S5" s="81"/>
-      <c r="T5" s="81"/>
-      <c r="U5" s="81"/>
-      <c r="V5" s="81"/>
-      <c r="W5" s="81"/>
-      <c r="X5" s="81" t="s">
+      <c r="R5" s="80"/>
+      <c r="S5" s="80"/>
+      <c r="T5" s="80"/>
+      <c r="U5" s="80"/>
+      <c r="V5" s="80"/>
+      <c r="W5" s="80"/>
+      <c r="X5" s="80" t="s">
         <v>109</v>
       </c>
-      <c r="Y5" s="81" t="s">
+      <c r="Y5" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="Z5" s="81"/>
-      <c r="AA5" s="80" t="s">
+      <c r="Z5" s="80"/>
+      <c r="AA5" t="s">
         <v>43</v>
       </c>
-      <c r="AB5" s="80" t="s">
+      <c r="AB5" t="s">
         <v>135</v>
       </c>
-      <c r="AC5" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD5" s="81" t="s">
+      <c r="AC5" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="AE5" s="81"/>
-      <c r="AF5" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG5" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM5" s="81" t="s">
+      <c r="AE5" s="80"/>
+      <c r="AF5" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG5" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM5" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="AN5" s="81" t="s">
+      <c r="AN5" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="AO5" s="81" t="s">
+      <c r="AO5" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="AP5" s="81">
+      <c r="AP5" s="80">
         <v>1765</v>
       </c>
-      <c r="AQ5" s="81" t="s">
+      <c r="AQ5" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="AR5" s="81" t="s">
+      <c r="AR5" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="AS5" s="81" t="s">
+      <c r="AS5" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="AT5" s="81"/>
-      <c r="AU5" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV5" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AW5" s="81" t="s">
+      <c r="AT5" s="80"/>
+      <c r="AU5" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV5" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW5" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="AZ5" s="81" t="s">
+      <c r="AZ5" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="BA5" s="81" t="s">
+      <c r="BA5" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="BB5" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC5" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD5" s="81"/>
-      <c r="BE5" s="81" t="s">
+      <c r="BB5" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC5" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD5" s="80"/>
+      <c r="BE5" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="BF5" s="81" t="s">
+      <c r="BF5" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="BG5" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BH5" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BI5" s="81"/>
-      <c r="BJ5" s="81" t="s">
+      <c r="BG5" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH5" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BI5" s="80"/>
+      <c r="BJ5" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="BK5" s="81" t="s">
+      <c r="BK5" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="BL5" s="81"/>
-      <c r="BM5" s="81" t="s">
+      <c r="BL5" s="80"/>
+      <c r="BM5" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="BN5" s="81" t="s">
+      <c r="BN5" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="BO5" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BP5" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BQ5" s="81"/>
-      <c r="BR5" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="BS5" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="BT5" s="81" t="s">
+      <c r="BO5" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP5" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BQ5" s="80"/>
+      <c r="BR5" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS5" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="BT5" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="BU5" s="81" t="s">
+      <c r="BU5" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="BV5" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="BW5" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="BX5" s="82"/>
-      <c r="BY5" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="BZ5" s="82" t="s">
+      <c r="BV5" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW5" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="BX5" s="81"/>
+      <c r="BY5" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="BZ5" s="81" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:467" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="85">
+    <row r="6" spans="1:467" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:467" x14ac:dyDescent="0.25">
-      <c r="A7" s="81" t="s">
+      <c r="A7" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="81" t="s">
+      <c r="B7" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81" t="s">
+      <c r="C7" s="80"/>
+      <c r="D7" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="81" t="s">
+      <c r="E7" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="81"/>
-      <c r="O7" s="81" t="s">
+      <c r="F7" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="80"/>
+      <c r="O7" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="P7" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q7" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R7" s="81"/>
-      <c r="S7" s="81" t="s">
+      <c r="P7" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R7" s="80"/>
+      <c r="S7" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="T7" s="81" t="s">
+      <c r="T7" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="U7" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="V7" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="W7" s="82"/>
-      <c r="X7" s="81" t="s">
+      <c r="U7" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="W7" s="81"/>
+      <c r="X7" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="Y7" s="80" t="s">
+      <c r="Y7" t="s">
         <v>61</v>
       </c>
-      <c r="AB7" s="81" t="s">
+      <c r="AB7" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AC7" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD7" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE7" s="82"/>
-      <c r="AF7" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG7" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM7" s="81" t="s">
+      <c r="AC7" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD7" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE7" s="81"/>
+      <c r="AF7" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG7" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM7" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="AN7" s="81" t="s">
+      <c r="AN7" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO7" s="81" t="s">
+      <c r="AO7" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="AP7" s="81">
+      <c r="AP7" s="80">
         <v>1790</v>
       </c>
-      <c r="AQ7" s="81" t="s">
+      <c r="AQ7" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="AR7" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS7" s="81" t="s">
+      <c r="AR7" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS7" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="AT7" s="81"/>
-      <c r="AU7" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV7" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ7" s="81" t="s">
+      <c r="AT7" s="80"/>
+      <c r="AU7" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV7" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ7" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="BA7" s="81" t="s">
+      <c r="BA7" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="BB7" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC7" s="81" t="s">
+      <c r="BB7" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC7" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="BD7" s="81"/>
-      <c r="BE7" s="81"/>
-      <c r="BF7" s="81" t="s">
+      <c r="BD7" s="80"/>
+      <c r="BE7" s="80"/>
+      <c r="BF7" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="BG7" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BH7" s="81" t="s">
+      <c r="BG7" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH7" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="BI7" s="81"/>
-      <c r="BJ7" s="81" t="s">
+      <c r="BI7" s="80"/>
+      <c r="BJ7" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="BK7" s="81" t="s">
+      <c r="BK7" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="BL7" s="81"/>
-      <c r="BM7" s="86" t="s">
+      <c r="BL7" s="80"/>
+      <c r="BM7" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="BN7" s="80" t="s">
+      <c r="BN7" t="s">
         <v>135</v>
       </c>
-      <c r="BO7" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BP7" s="81" t="s">
+      <c r="BO7" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP7" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="BQ7" s="81"/>
-      <c r="BR7" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="BS7" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CA7" s="81" t="s">
+      <c r="BQ7" s="80"/>
+      <c r="BR7" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS7" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CA7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="CB7" s="81" t="s">
+      <c r="CB7" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="CC7" s="81" t="s">
+      <c r="CC7" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="CD7" s="81">
+      <c r="CD7" s="80">
         <v>1765</v>
       </c>
-      <c r="CE7" s="81" t="s">
+      <c r="CE7" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="CF7" s="81" t="s">
+      <c r="CF7" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="CG7" s="81" t="s">
+      <c r="CG7" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="CH7" s="81"/>
-      <c r="CI7" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ7" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CK7" s="81" t="s">
+      <c r="CH7" s="80"/>
+      <c r="CI7" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ7" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CK7" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="CN7" s="81" t="s">
+      <c r="CN7" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="CO7" s="81" t="s">
+      <c r="CO7" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="CP7" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ7" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="CR7" s="81"/>
-      <c r="CS7" s="81" t="s">
+      <c r="CP7" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ7" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="CR7" s="80"/>
+      <c r="CS7" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="CT7" s="81" t="s">
+      <c r="CT7" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="CU7" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV7" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="CW7" s="81" t="s">
+      <c r="CU7" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV7" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="CW7" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="CX7" s="81" t="s">
+      <c r="CX7" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="CY7" s="81"/>
-      <c r="CZ7" s="81" t="s">
+      <c r="CY7" s="80"/>
+      <c r="CZ7" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="DA7" s="81" t="s">
+      <c r="DA7" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="DB7" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC7" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="DD7" s="81"/>
-      <c r="DE7" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF7" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DG7" s="81" t="s">
+      <c r="DB7" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC7" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="DD7" s="80"/>
+      <c r="DE7" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF7" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DG7" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="DH7" s="81" t="s">
+      <c r="DH7" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="DI7" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="DJ7" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="DK7" s="82"/>
-      <c r="DL7" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DM7" s="82" t="s">
+      <c r="DI7" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="DJ7" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="DK7" s="81"/>
+      <c r="DL7" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DM7" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:467" x14ac:dyDescent="0.25">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="81" t="s">
+      <c r="B8" s="80" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81" t="s">
+      <c r="C8" s="80"/>
+      <c r="D8" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="81" t="s">
+      <c r="E8" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N8" s="81"/>
-      <c r="O8" s="81"/>
-      <c r="P8" s="81"/>
-      <c r="Q8" s="81"/>
-      <c r="R8" s="81"/>
-      <c r="S8" s="81" t="s">
+      <c r="F8" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" s="80"/>
+      <c r="O8" s="80"/>
+      <c r="P8" s="80"/>
+      <c r="Q8" s="80"/>
+      <c r="R8" s="80"/>
+      <c r="S8" s="80" t="s">
         <v>139</v>
       </c>
-      <c r="T8" s="81" t="s">
+      <c r="T8" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="U8" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="V8" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="W8" s="82"/>
-      <c r="X8" s="81" t="s">
+      <c r="U8" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="V8" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="W8" s="81"/>
+      <c r="X8" s="80" t="s">
         <v>137</v>
       </c>
-      <c r="Y8" s="81" t="s">
+      <c r="Y8" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="Z8" s="81"/>
-      <c r="AA8" s="80" t="s">
+      <c r="Z8" s="80"/>
+      <c r="AA8" t="s">
         <v>138</v>
       </c>
-      <c r="AB8" s="81" t="s">
+      <c r="AB8" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AC8" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD8" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE8" s="82"/>
-      <c r="AF8" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG8" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM8" s="81" t="s">
+      <c r="AC8" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD8" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE8" s="81"/>
+      <c r="AF8" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG8" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM8" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="AN8" s="81" t="s">
+      <c r="AN8" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="AO8" s="81" t="s">
+      <c r="AO8" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="AP8" s="81" t="s">
+      <c r="AP8" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="AQ8" s="81" t="s">
+      <c r="AQ8" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="AR8" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS8" s="81" t="s">
+      <c r="AR8" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS8" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="AT8" s="81"/>
-      <c r="AU8" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV8" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ8" s="81" t="s">
+      <c r="AT8" s="80"/>
+      <c r="AU8" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV8" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ8" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="BA8" s="81" t="s">
+      <c r="BA8" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="BB8" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC8" s="81" t="s">
+      <c r="BB8" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC8" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="BD8" s="81"/>
-      <c r="BE8" s="81"/>
-      <c r="BF8" s="81"/>
-      <c r="BG8" s="81"/>
-      <c r="BH8" s="81"/>
-      <c r="BI8" s="81"/>
-      <c r="BJ8" s="81" t="s">
+      <c r="BD8" s="80"/>
+      <c r="BE8" s="80"/>
+      <c r="BF8" s="80"/>
+      <c r="BG8" s="80"/>
+      <c r="BH8" s="80"/>
+      <c r="BI8" s="80"/>
+      <c r="BJ8" s="80" t="s">
         <v>109</v>
       </c>
-      <c r="BK8" s="81" t="s">
+      <c r="BK8" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="BL8" s="81"/>
-      <c r="BM8" s="80" t="s">
+      <c r="BL8" s="80"/>
+      <c r="BM8" t="s">
         <v>43</v>
       </c>
-      <c r="BN8" s="80" t="s">
+      <c r="BN8" t="s">
         <v>135</v>
       </c>
-      <c r="BO8" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BP8" s="81" t="s">
+      <c r="BO8" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP8" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="BQ8" s="81"/>
-      <c r="BR8" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="BS8" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CA8" s="81" t="s">
+      <c r="BQ8" s="80"/>
+      <c r="BR8" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS8" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CA8" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="CB8" s="81" t="s">
+      <c r="CB8" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="CC8" s="81" t="s">
+      <c r="CC8" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="CD8" s="81">
+      <c r="CD8" s="80">
         <v>1765</v>
       </c>
-      <c r="CE8" s="81" t="s">
+      <c r="CE8" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="CF8" s="81" t="s">
+      <c r="CF8" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="CG8" s="81" t="s">
+      <c r="CG8" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="CH8" s="81"/>
-      <c r="CI8" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ8" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CK8" s="81" t="s">
+      <c r="CH8" s="80"/>
+      <c r="CI8" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ8" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CK8" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="CN8" s="81" t="s">
+      <c r="CN8" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="CO8" s="81" t="s">
+      <c r="CO8" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="CP8" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ8" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="CR8" s="81"/>
-      <c r="CS8" s="81" t="s">
+      <c r="CP8" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ8" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="CR8" s="80"/>
+      <c r="CS8" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="CT8" s="81" t="s">
+      <c r="CT8" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="CU8" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV8" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="CW8" s="81" t="s">
+      <c r="CU8" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV8" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="CW8" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="CX8" s="81" t="s">
+      <c r="CX8" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="CY8" s="81"/>
-      <c r="CZ8" s="81" t="s">
+      <c r="CY8" s="80"/>
+      <c r="CZ8" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="DA8" s="81" t="s">
+      <c r="DA8" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="DB8" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC8" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="DD8" s="81"/>
-      <c r="DE8" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF8" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DG8" s="81" t="s">
+      <c r="DB8" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC8" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="DD8" s="80"/>
+      <c r="DE8" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF8" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DG8" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="DH8" s="81" t="s">
+      <c r="DH8" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="DI8" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="DJ8" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="DK8" s="82"/>
-      <c r="DL8" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DM8" s="82" t="s">
+      <c r="DI8" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="DJ8" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="DK8" s="81"/>
+      <c r="DL8" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DM8" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:467" x14ac:dyDescent="0.25">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81" t="s">
+      <c r="C9" s="80"/>
+      <c r="D9" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="E9" s="81" t="s">
+      <c r="E9" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N9" s="81"/>
-      <c r="O9" s="81" t="s">
+      <c r="F9" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="80"/>
+      <c r="O9" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="P9" s="81"/>
-      <c r="Q9" s="81"/>
-      <c r="R9" s="81"/>
-      <c r="S9" s="81"/>
-      <c r="T9" s="81"/>
-      <c r="U9" s="81"/>
-      <c r="V9" s="81"/>
-      <c r="W9" s="81"/>
-      <c r="X9" s="81" t="s">
+      <c r="P9" s="80"/>
+      <c r="Q9" s="80"/>
+      <c r="R9" s="80"/>
+      <c r="S9" s="80"/>
+      <c r="T9" s="80"/>
+      <c r="U9" s="80"/>
+      <c r="V9" s="80"/>
+      <c r="W9" s="80"/>
+      <c r="X9" s="80" t="s">
         <v>111</v>
       </c>
-      <c r="Y9" s="80" t="s">
+      <c r="Y9" t="s">
         <v>112</v>
       </c>
-      <c r="AB9" s="81" t="s">
+      <c r="AB9" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AC9" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD9" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE9" s="82"/>
-      <c r="AF9" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG9" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM9" s="81" t="s">
+      <c r="AC9" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD9" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE9" s="81"/>
+      <c r="AF9" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG9" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM9" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="AN9" s="81" t="s">
+      <c r="AN9" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO9" s="81" t="s">
+      <c r="AO9" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="AP9" s="81">
+      <c r="AP9" s="80">
         <v>1790</v>
       </c>
-      <c r="AQ9" s="81" t="s">
+      <c r="AQ9" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="AR9" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS9" s="81" t="s">
+      <c r="AR9" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS9" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="AT9" s="81"/>
-      <c r="AU9" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV9" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ9" s="81" t="s">
+      <c r="AT9" s="80"/>
+      <c r="AU9" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV9" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ9" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="BA9" s="81" t="s">
+      <c r="BA9" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="BB9" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC9" s="81" t="s">
+      <c r="BB9" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC9" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="BD9" s="81"/>
-      <c r="BE9" s="81"/>
-      <c r="BF9" s="81" t="s">
+      <c r="BD9" s="80"/>
+      <c r="BE9" s="80"/>
+      <c r="BF9" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="BG9" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BH9" s="81" t="s">
+      <c r="BG9" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH9" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="BI9" s="81"/>
-      <c r="BJ9" s="81" t="s">
+      <c r="BI9" s="80"/>
+      <c r="BJ9" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="BK9" s="81" t="s">
+      <c r="BK9" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="BL9" s="81"/>
-      <c r="BM9" s="86" t="s">
+      <c r="BL9" s="80"/>
+      <c r="BM9" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="BN9" s="80" t="s">
+      <c r="BN9" t="s">
         <v>135</v>
       </c>
-      <c r="BO9" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BP9" s="81" t="s">
+      <c r="BO9" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP9" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="BQ9" s="81"/>
-      <c r="BR9" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="BS9" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CA9" s="81" t="s">
+      <c r="BQ9" s="80"/>
+      <c r="BR9" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS9" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CA9" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="CB9" s="81" t="s">
+      <c r="CB9" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="CC9" s="81" t="s">
+      <c r="CC9" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="CD9" s="81">
+      <c r="CD9" s="80">
         <v>1765</v>
       </c>
-      <c r="CE9" s="81" t="s">
+      <c r="CE9" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="CF9" s="81" t="s">
+      <c r="CF9" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="CG9" s="81" t="s">
+      <c r="CG9" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="CH9" s="81"/>
-      <c r="CI9" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ9" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CK9" s="81" t="s">
+      <c r="CH9" s="80"/>
+      <c r="CI9" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ9" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CK9" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="CN9" s="81" t="s">
+      <c r="CN9" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="CO9" s="81" t="s">
+      <c r="CO9" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="CP9" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ9" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="CR9" s="81"/>
-      <c r="CS9" s="81" t="s">
+      <c r="CP9" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ9" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="CR9" s="80"/>
+      <c r="CS9" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="CT9" s="81" t="s">
+      <c r="CT9" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="CU9" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV9" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="CW9" s="81" t="s">
+      <c r="CU9" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV9" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="CW9" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="CX9" s="81" t="s">
+      <c r="CX9" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="CY9" s="81"/>
-      <c r="CZ9" s="81" t="s">
+      <c r="CY9" s="80"/>
+      <c r="CZ9" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="DA9" s="81" t="s">
+      <c r="DA9" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="DB9" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC9" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="DD9" s="81"/>
-      <c r="DE9" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF9" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DG9" s="81" t="s">
+      <c r="DB9" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC9" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="DD9" s="80"/>
+      <c r="DE9" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF9" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DG9" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="DH9" s="81" t="s">
+      <c r="DH9" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="DI9" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="DJ9" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="DK9" s="82"/>
-      <c r="DL9" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DM9" s="82" t="s">
+      <c r="DI9" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="DJ9" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="DK9" s="81"/>
+      <c r="DL9" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DM9" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:467" x14ac:dyDescent="0.25">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="81" t="s">
+      <c r="B10" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81">
+      <c r="C10" s="80"/>
+      <c r="D10" s="80">
         <v>1832</v>
       </c>
-      <c r="E10" s="81" t="s">
+      <c r="E10" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N10" s="81"/>
-      <c r="O10" s="81"/>
-      <c r="P10" s="81"/>
-      <c r="Q10" s="81"/>
-      <c r="R10" s="81"/>
-      <c r="S10" s="81"/>
-      <c r="T10" s="81"/>
-      <c r="U10" s="81"/>
-      <c r="V10" s="81"/>
-      <c r="W10" s="81"/>
-      <c r="X10" s="81"/>
-      <c r="Y10" s="81"/>
-      <c r="Z10" s="81"/>
-      <c r="AB10" s="81"/>
-      <c r="AC10" s="81"/>
-      <c r="AD10" s="81"/>
-      <c r="AE10" s="81"/>
-      <c r="AF10" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG10" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM10" s="81" t="s">
+      <c r="F10" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" s="80"/>
+      <c r="O10" s="80"/>
+      <c r="P10" s="80"/>
+      <c r="Q10" s="80"/>
+      <c r="R10" s="80"/>
+      <c r="S10" s="80"/>
+      <c r="T10" s="80"/>
+      <c r="U10" s="80"/>
+      <c r="V10" s="80"/>
+      <c r="W10" s="80"/>
+      <c r="X10" s="80"/>
+      <c r="Y10" s="80"/>
+      <c r="Z10" s="80"/>
+      <c r="AB10" s="80"/>
+      <c r="AC10" s="80"/>
+      <c r="AD10" s="80"/>
+      <c r="AE10" s="80"/>
+      <c r="AF10" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG10" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM10" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="AN10" s="81" t="s">
+      <c r="AN10" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="AO10" s="81" t="s">
+      <c r="AO10" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="AP10" s="81" t="s">
+      <c r="AP10" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="AQ10" s="81" t="s">
+      <c r="AQ10" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="AR10" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS10" s="81" t="s">
+      <c r="AR10" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS10" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="AT10" s="81"/>
-      <c r="AU10" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV10" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ10" s="81" t="s">
+      <c r="AT10" s="80"/>
+      <c r="AU10" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV10" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ10" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="BA10" s="81" t="s">
+      <c r="BA10" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="BB10" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC10" s="81" t="s">
+      <c r="BB10" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC10" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="BD10" s="81"/>
-      <c r="BE10" s="81"/>
-      <c r="BF10" s="81"/>
-      <c r="BG10" s="81"/>
-      <c r="BH10" s="81"/>
-      <c r="BI10" s="81"/>
-      <c r="BJ10" s="81" t="s">
+      <c r="BD10" s="80"/>
+      <c r="BE10" s="80"/>
+      <c r="BF10" s="80"/>
+      <c r="BG10" s="80"/>
+      <c r="BH10" s="80"/>
+      <c r="BI10" s="80"/>
+      <c r="BJ10" s="80" t="s">
         <v>109</v>
       </c>
-      <c r="BK10" s="81" t="s">
+      <c r="BK10" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="BL10" s="81"/>
-      <c r="BM10" s="80" t="s">
+      <c r="BL10" s="80"/>
+      <c r="BM10" t="s">
         <v>43</v>
       </c>
-      <c r="BN10" s="80" t="s">
+      <c r="BN10" t="s">
         <v>135</v>
       </c>
-      <c r="BO10" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BP10" s="81" t="s">
+      <c r="BO10" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP10" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="BQ10" s="81"/>
-      <c r="BR10" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="BS10" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CA10" s="81" t="s">
+      <c r="BQ10" s="80"/>
+      <c r="BR10" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS10" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CA10" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="CB10" s="81" t="s">
+      <c r="CB10" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="CC10" s="81" t="s">
+      <c r="CC10" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="CD10" s="81">
+      <c r="CD10" s="80">
         <v>1765</v>
       </c>
-      <c r="CE10" s="81" t="s">
+      <c r="CE10" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="CF10" s="81" t="s">
+      <c r="CF10" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="CG10" s="81" t="s">
+      <c r="CG10" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="CH10" s="81"/>
-      <c r="CI10" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ10" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CK10" s="81" t="s">
+      <c r="CH10" s="80"/>
+      <c r="CI10" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ10" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CK10" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="CN10" s="81" t="s">
+      <c r="CN10" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="CO10" s="81" t="s">
+      <c r="CO10" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="CP10" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ10" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="CR10" s="81"/>
-      <c r="CS10" s="81" t="s">
+      <c r="CP10" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ10" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="CR10" s="80"/>
+      <c r="CS10" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="CT10" s="81" t="s">
+      <c r="CT10" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="CU10" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV10" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="CW10" s="81" t="s">
+      <c r="CU10" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV10" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="CW10" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="CX10" s="81" t="s">
+      <c r="CX10" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="CY10" s="81"/>
-      <c r="CZ10" s="81" t="s">
+      <c r="CY10" s="80"/>
+      <c r="CZ10" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="DA10" s="81" t="s">
+      <c r="DA10" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="DB10" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC10" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="DD10" s="81"/>
-      <c r="DE10" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF10" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DG10" s="81" t="s">
+      <c r="DB10" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC10" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="DD10" s="80"/>
+      <c r="DE10" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF10" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DG10" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="DH10" s="81" t="s">
+      <c r="DH10" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="DI10" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="DJ10" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="DK10" s="82"/>
-      <c r="DL10" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DM10" s="82" t="s">
+      <c r="DI10" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="DJ10" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="DK10" s="81"/>
+      <c r="DL10" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DM10" s="81" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:467" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="85">
+    <row r="11" spans="1:467" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:467" x14ac:dyDescent="0.25">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="81" t="s">
+      <c r="C12" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="81" t="s">
+      <c r="D12" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="81" t="s">
+      <c r="E12" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="82"/>
-      <c r="I12" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N12" s="81"/>
-      <c r="O12" s="81" t="s">
+      <c r="F12" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" s="80"/>
+      <c r="O12" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="P12" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q12" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R12" s="81"/>
-      <c r="S12" s="81"/>
-      <c r="T12" s="81"/>
-      <c r="U12" s="81"/>
-      <c r="V12" s="81"/>
-      <c r="W12" s="81"/>
-      <c r="X12" s="81"/>
-      <c r="Y12" s="81"/>
-      <c r="Z12" s="81"/>
-      <c r="AM12" s="81" t="s">
+      <c r="P12" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R12" s="80"/>
+      <c r="S12" s="80"/>
+      <c r="T12" s="80"/>
+      <c r="U12" s="80"/>
+      <c r="V12" s="80"/>
+      <c r="W12" s="80"/>
+      <c r="X12" s="80"/>
+      <c r="Y12" s="80"/>
+      <c r="Z12" s="80"/>
+      <c r="AM12" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="AN12" s="81" t="s">
+      <c r="AN12" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO12" s="81"/>
-      <c r="AP12" s="81" t="s">
+      <c r="AO12" s="80"/>
+      <c r="AP12" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AQ12" s="81" t="s">
+      <c r="AQ12" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AR12" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS12" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT12" s="82"/>
-      <c r="AU12" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV12" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ12" s="81"/>
-      <c r="BA12" s="81" t="s">
+      <c r="AR12" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS12" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT12" s="81"/>
+      <c r="AU12" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV12" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ12" s="80"/>
+      <c r="BA12" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="BB12" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC12" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD12" s="81"/>
-      <c r="BE12" s="81" t="s">
+      <c r="BB12" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC12" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD12" s="80"/>
+      <c r="BE12" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="BF12" s="81"/>
-      <c r="BG12" s="81"/>
-      <c r="BH12" s="81"/>
-      <c r="BI12" s="81"/>
-      <c r="BJ12" s="81" t="s">
+      <c r="BF12" s="80"/>
+      <c r="BG12" s="80"/>
+      <c r="BH12" s="80"/>
+      <c r="BI12" s="80"/>
+      <c r="BJ12" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="BK12" s="80" t="s">
+      <c r="BK12" t="s">
         <v>61</v>
       </c>
-      <c r="CA12" s="81" t="s">
+      <c r="CA12" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="CB12" s="81" t="s">
+      <c r="CB12" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="CC12" s="81" t="s">
+      <c r="CC12" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="CD12" s="81">
+      <c r="CD12" s="80">
         <v>1790</v>
       </c>
-      <c r="CE12" s="81" t="s">
+      <c r="CE12" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CF12" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG12" s="81" t="s">
+      <c r="CF12" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG12" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CH12" s="81"/>
-      <c r="CI12" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ12" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CN12" s="81" t="s">
+      <c r="CH12" s="80"/>
+      <c r="CI12" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ12" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CN12" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="CO12" s="81" t="s">
+      <c r="CO12" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CP12" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ12" s="81" t="s">
+      <c r="CP12" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ12" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CR12" s="81"/>
-      <c r="CS12" s="81"/>
-      <c r="CT12" s="81" t="s">
+      <c r="CR12" s="80"/>
+      <c r="CS12" s="80"/>
+      <c r="CT12" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="CU12" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV12" s="81" t="s">
+      <c r="CU12" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV12" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="CW12" s="81" t="s">
+      <c r="CW12" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="CX12" s="81" t="s">
+      <c r="CX12" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="CY12" s="81"/>
-      <c r="CZ12" s="86" t="s">
+      <c r="CY12" s="80"/>
+      <c r="CZ12" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="DA12" s="80" t="s">
+      <c r="DA12" t="s">
         <v>135</v>
       </c>
-      <c r="DB12" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC12" s="81" t="s">
+      <c r="DB12" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC12" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="DD12" s="81"/>
-      <c r="DE12" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF12" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DN12" s="81" t="s">
+      <c r="DD12" s="80"/>
+      <c r="DE12" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF12" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DN12" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DO12" s="81" t="s">
+      <c r="DO12" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="DP12" s="81" t="s">
+      <c r="DP12" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="DQ12" s="81">
+      <c r="DQ12" s="80">
         <v>1765</v>
       </c>
-      <c r="DR12" s="81" t="s">
+      <c r="DR12" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="DS12" s="81" t="s">
+      <c r="DS12" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="DT12" s="81" t="s">
+      <c r="DT12" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="DU12" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DV12" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DW12" s="81" t="s">
+      <c r="DU12" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DV12" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DW12" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="DZ12" s="81" t="s">
+      <c r="DZ12" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="EA12" s="81" t="s">
+      <c r="EA12" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EB12" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EC12" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="ED12" s="81" t="s">
+      <c r="EB12" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC12" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="ED12" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="EE12" s="81" t="s">
+      <c r="EE12" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EF12" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EG12" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EH12" s="81" t="s">
+      <c r="EF12" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EG12" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EH12" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="EI12" s="81" t="s">
+      <c r="EI12" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="EJ12" s="81" t="s">
+      <c r="EJ12" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="EK12" s="81"/>
-      <c r="EL12" s="81" t="s">
+      <c r="EK12" s="80"/>
+      <c r="EL12" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="EM12" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EN12" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EO12" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EP12" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="EQ12" s="81" t="s">
+      <c r="EM12" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EN12" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EO12" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EP12" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ12" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="ER12" s="81" t="s">
+      <c r="ER12" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="ES12" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="ET12" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="EU12" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EV12" s="82" t="s">
+      <c r="ES12" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="ET12" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="EU12" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EV12" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:467" x14ac:dyDescent="0.25">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="81" t="s">
+      <c r="B13" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81" t="s">
+      <c r="C13" s="80"/>
+      <c r="D13" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="81" t="s">
+      <c r="E13" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N13" s="81" t="s">
+      <c r="F13" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N13" s="80" t="s">
         <v>65</v>
       </c>
-      <c r="O13" s="81" t="s">
+      <c r="O13" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="P13" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q13" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R13" s="81"/>
-      <c r="S13" s="81"/>
-      <c r="T13" s="81"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="81"/>
-      <c r="W13" s="81"/>
-      <c r="X13" s="81"/>
-      <c r="Y13" s="81"/>
-      <c r="Z13" s="81"/>
-      <c r="AM13" s="81" t="s">
+      <c r="P13" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R13" s="80"/>
+      <c r="S13" s="80"/>
+      <c r="T13" s="80"/>
+      <c r="U13" s="80"/>
+      <c r="V13" s="80"/>
+      <c r="W13" s="80"/>
+      <c r="X13" s="80"/>
+      <c r="Y13" s="80"/>
+      <c r="Z13" s="80"/>
+      <c r="AM13" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="AN13" s="81" t="s">
+      <c r="AN13" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO13" s="81"/>
-      <c r="AP13" s="81" t="s">
+      <c r="AO13" s="80"/>
+      <c r="AP13" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AQ13" s="81" t="s">
+      <c r="AQ13" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AR13" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS13" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT13" s="82"/>
-      <c r="AU13" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV13" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ13" s="81"/>
-      <c r="BA13" s="81" t="s">
+      <c r="AR13" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS13" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT13" s="81"/>
+      <c r="AU13" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV13" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ13" s="80"/>
+      <c r="BA13" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="BB13" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC13" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD13" s="81"/>
-      <c r="BE13" s="81" t="s">
+      <c r="BB13" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC13" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD13" s="80"/>
+      <c r="BE13" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="BF13" s="81"/>
-      <c r="BG13" s="81"/>
-      <c r="BH13" s="81"/>
-      <c r="BI13" s="81"/>
-      <c r="BJ13" s="81" t="s">
+      <c r="BF13" s="80"/>
+      <c r="BG13" s="80"/>
+      <c r="BH13" s="80"/>
+      <c r="BI13" s="80"/>
+      <c r="BJ13" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="BK13" s="80" t="s">
+      <c r="BK13" t="s">
         <v>61</v>
       </c>
-      <c r="CA13" s="81" t="s">
+      <c r="CA13" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="CB13" s="81" t="s">
+      <c r="CB13" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="CC13" s="81" t="s">
+      <c r="CC13" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="CD13" s="81">
+      <c r="CD13" s="80">
         <v>1790</v>
       </c>
-      <c r="CE13" s="81" t="s">
+      <c r="CE13" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CF13" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG13" s="81" t="s">
+      <c r="CF13" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG13" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CH13" s="81"/>
-      <c r="CI13" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ13" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CN13" s="81" t="s">
+      <c r="CH13" s="80"/>
+      <c r="CI13" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ13" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CN13" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="CO13" s="81" t="s">
+      <c r="CO13" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CP13" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ13" s="81" t="s">
+      <c r="CP13" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ13" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CR13" s="81"/>
-      <c r="CS13" s="81"/>
-      <c r="CT13" s="81" t="s">
+      <c r="CR13" s="80"/>
+      <c r="CS13" s="80"/>
+      <c r="CT13" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="CU13" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV13" s="81" t="s">
+      <c r="CU13" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV13" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="CW13" s="81" t="s">
+      <c r="CW13" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="CX13" s="81" t="s">
+      <c r="CX13" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="CY13" s="81"/>
-      <c r="CZ13" s="86" t="s">
+      <c r="CY13" s="80"/>
+      <c r="CZ13" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="DA13" s="80" t="s">
+      <c r="DA13" t="s">
         <v>135</v>
       </c>
-      <c r="DB13" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC13" s="81" t="s">
+      <c r="DB13" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC13" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="DD13" s="81"/>
-      <c r="DE13" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF13" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DN13" s="81" t="s">
+      <c r="DD13" s="80"/>
+      <c r="DE13" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF13" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DN13" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DO13" s="81" t="s">
+      <c r="DO13" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="DP13" s="81" t="s">
+      <c r="DP13" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="DQ13" s="81">
+      <c r="DQ13" s="80">
         <v>1765</v>
       </c>
-      <c r="DR13" s="81" t="s">
+      <c r="DR13" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="DS13" s="81" t="s">
+      <c r="DS13" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="DT13" s="81" t="s">
+      <c r="DT13" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="DU13" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DV13" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DW13" s="81" t="s">
+      <c r="DU13" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DV13" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DW13" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="DZ13" s="81" t="s">
+      <c r="DZ13" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="EA13" s="81" t="s">
+      <c r="EA13" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EB13" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EC13" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="ED13" s="81" t="s">
+      <c r="EB13" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC13" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="ED13" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="EE13" s="81" t="s">
+      <c r="EE13" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EF13" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EG13" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EH13" s="81" t="s">
+      <c r="EF13" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EG13" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EH13" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="EI13" s="81" t="s">
+      <c r="EI13" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="EJ13" s="81" t="s">
+      <c r="EJ13" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="EK13" s="81"/>
-      <c r="EL13" s="81" t="s">
+      <c r="EK13" s="80"/>
+      <c r="EL13" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="EM13" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EN13" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EO13" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EP13" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="EQ13" s="81" t="s">
+      <c r="EM13" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EN13" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EO13" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EP13" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ13" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="ER13" s="81" t="s">
+      <c r="ER13" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="ES13" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="ET13" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="EU13" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EV13" s="82" t="s">
+      <c r="ES13" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="ET13" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="EU13" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EV13" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:467" x14ac:dyDescent="0.25">
-      <c r="A14" s="81" t="s">
+      <c r="A14" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="81" t="s">
+      <c r="B14" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="81"/>
-      <c r="D14" s="81" t="s">
+      <c r="C14" s="80"/>
+      <c r="D14" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="81" t="s">
+      <c r="E14" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="82"/>
-      <c r="I14" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" s="81" t="s">
+      <c r="F14" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="N14" s="81"/>
-      <c r="O14" s="81" t="s">
+      <c r="N14" s="80"/>
+      <c r="O14" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="P14" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q14" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R14" s="81"/>
-      <c r="S14" s="81"/>
-      <c r="T14" s="81"/>
-      <c r="U14" s="81"/>
-      <c r="V14" s="81"/>
-      <c r="W14" s="81"/>
-      <c r="X14" s="81" t="s">
+      <c r="P14" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R14" s="80"/>
+      <c r="S14" s="80"/>
+      <c r="T14" s="80"/>
+      <c r="U14" s="80"/>
+      <c r="V14" s="80"/>
+      <c r="W14" s="80"/>
+      <c r="X14" s="80" t="s">
         <v>116</v>
       </c>
-      <c r="Y14" s="80" t="s">
+      <c r="Y14" t="s">
         <v>36</v>
       </c>
-      <c r="AM14" s="81" t="s">
+      <c r="AM14" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="AN14" s="81" t="s">
+      <c r="AN14" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO14" s="81"/>
-      <c r="AP14" s="81" t="s">
+      <c r="AO14" s="80"/>
+      <c r="AP14" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AQ14" s="81" t="s">
+      <c r="AQ14" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AR14" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS14" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT14" s="82"/>
-      <c r="AU14" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV14" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ14" s="81"/>
-      <c r="BA14" s="81" t="s">
+      <c r="AR14" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS14" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT14" s="81"/>
+      <c r="AU14" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV14" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ14" s="80"/>
+      <c r="BA14" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="BB14" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC14" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD14" s="81"/>
-      <c r="BE14" s="81" t="s">
+      <c r="BB14" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC14" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD14" s="80"/>
+      <c r="BE14" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="BF14" s="81"/>
-      <c r="BG14" s="81"/>
-      <c r="BH14" s="81"/>
-      <c r="BI14" s="81"/>
-      <c r="BJ14" s="81" t="s">
+      <c r="BF14" s="80"/>
+      <c r="BG14" s="80"/>
+      <c r="BH14" s="80"/>
+      <c r="BI14" s="80"/>
+      <c r="BJ14" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="BK14" s="80" t="s">
+      <c r="BK14" t="s">
         <v>61</v>
       </c>
-      <c r="CA14" s="81" t="s">
+      <c r="CA14" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="CB14" s="81" t="s">
+      <c r="CB14" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="CC14" s="81" t="s">
+      <c r="CC14" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="CD14" s="81">
+      <c r="CD14" s="80">
         <v>1790</v>
       </c>
-      <c r="CE14" s="81" t="s">
+      <c r="CE14" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CF14" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG14" s="81" t="s">
+      <c r="CF14" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG14" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CH14" s="81"/>
-      <c r="CI14" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ14" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CN14" s="81" t="s">
+      <c r="CH14" s="80"/>
+      <c r="CI14" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ14" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CN14" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="CO14" s="81" t="s">
+      <c r="CO14" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CP14" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ14" s="81" t="s">
+      <c r="CP14" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ14" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CR14" s="81"/>
-      <c r="CS14" s="81"/>
-      <c r="CT14" s="81" t="s">
+      <c r="CR14" s="80"/>
+      <c r="CS14" s="80"/>
+      <c r="CT14" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="CU14" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV14" s="81" t="s">
+      <c r="CU14" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV14" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="CW14" s="81" t="s">
+      <c r="CW14" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="CX14" s="81" t="s">
+      <c r="CX14" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="CY14" s="81"/>
-      <c r="CZ14" s="86" t="s">
+      <c r="CY14" s="80"/>
+      <c r="CZ14" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="DA14" s="80" t="s">
+      <c r="DA14" t="s">
         <v>135</v>
       </c>
-      <c r="DB14" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC14" s="81" t="s">
+      <c r="DB14" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC14" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="DD14" s="81"/>
-      <c r="DE14" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF14" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DN14" s="81" t="s">
+      <c r="DD14" s="80"/>
+      <c r="DE14" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF14" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DN14" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DO14" s="81" t="s">
+      <c r="DO14" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="DP14" s="81" t="s">
+      <c r="DP14" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="DQ14" s="81">
+      <c r="DQ14" s="80">
         <v>1765</v>
       </c>
-      <c r="DR14" s="81" t="s">
+      <c r="DR14" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="DS14" s="81" t="s">
+      <c r="DS14" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="DT14" s="81" t="s">
+      <c r="DT14" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="DU14" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DV14" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DW14" s="81" t="s">
+      <c r="DU14" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DV14" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DW14" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="DZ14" s="81" t="s">
+      <c r="DZ14" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="EA14" s="81" t="s">
+      <c r="EA14" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EB14" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EC14" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="ED14" s="81" t="s">
+      <c r="EB14" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC14" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="ED14" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="EE14" s="81" t="s">
+      <c r="EE14" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EF14" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EG14" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EH14" s="81" t="s">
+      <c r="EF14" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EG14" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EH14" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="EI14" s="81" t="s">
+      <c r="EI14" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="EJ14" s="81" t="s">
+      <c r="EJ14" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="EK14" s="81"/>
-      <c r="EL14" s="81" t="s">
+      <c r="EK14" s="80"/>
+      <c r="EL14" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="EM14" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EN14" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EO14" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EP14" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="EQ14" s="81" t="s">
+      <c r="EM14" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EN14" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EO14" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EP14" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ14" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="ER14" s="81" t="s">
+      <c r="ER14" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="ES14" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="ET14" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="EU14" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EV14" s="82" t="s">
+      <c r="ES14" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="ET14" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="EU14" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EV14" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:467" x14ac:dyDescent="0.25">
-      <c r="A15" s="81" t="s">
+      <c r="A15" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="81"/>
-      <c r="D15" s="81" t="s">
+      <c r="C15" s="80"/>
+      <c r="D15" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="81" t="s">
+      <c r="E15" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="82"/>
-      <c r="I15" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N15" s="81"/>
-      <c r="O15" s="81" t="s">
+      <c r="F15" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="P15" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q15" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" s="81"/>
-      <c r="S15" s="81"/>
-      <c r="T15" s="81"/>
-      <c r="U15" s="81"/>
-      <c r="V15" s="81"/>
-      <c r="W15" s="81"/>
-      <c r="X15" s="81"/>
-      <c r="Y15" s="81"/>
-      <c r="Z15" s="81"/>
-      <c r="AM15" s="81" t="s">
+      <c r="P15" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q15" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R15" s="80"/>
+      <c r="S15" s="80"/>
+      <c r="T15" s="80"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="80"/>
+      <c r="W15" s="80"/>
+      <c r="X15" s="80"/>
+      <c r="Y15" s="80"/>
+      <c r="Z15" s="80"/>
+      <c r="AM15" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="AN15" s="81" t="s">
+      <c r="AN15" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO15" s="81"/>
-      <c r="AP15" s="81" t="s">
+      <c r="AO15" s="80"/>
+      <c r="AP15" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AQ15" s="81" t="s">
+      <c r="AQ15" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AR15" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS15" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT15" s="82"/>
-      <c r="AU15" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV15" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ15" s="81"/>
-      <c r="BA15" s="81" t="s">
+      <c r="AR15" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS15" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT15" s="81"/>
+      <c r="AU15" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV15" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ15" s="80"/>
+      <c r="BA15" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="BB15" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC15" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD15" s="81"/>
-      <c r="BE15" s="81" t="s">
+      <c r="BB15" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC15" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD15" s="80"/>
+      <c r="BE15" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="BF15" s="81"/>
-      <c r="BG15" s="81"/>
-      <c r="BH15" s="81"/>
-      <c r="BI15" s="81"/>
-      <c r="BJ15" s="81" t="s">
+      <c r="BF15" s="80"/>
+      <c r="BG15" s="80"/>
+      <c r="BH15" s="80"/>
+      <c r="BI15" s="80"/>
+      <c r="BJ15" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="BK15" s="80" t="s">
+      <c r="BK15" t="s">
         <v>61</v>
       </c>
-      <c r="CA15" s="81" t="s">
+      <c r="CA15" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="CB15" s="81" t="s">
+      <c r="CB15" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="CC15" s="81" t="s">
+      <c r="CC15" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="CD15" s="81">
+      <c r="CD15" s="80">
         <v>1790</v>
       </c>
-      <c r="CE15" s="81" t="s">
+      <c r="CE15" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CF15" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG15" s="81" t="s">
+      <c r="CF15" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG15" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CH15" s="81"/>
-      <c r="CI15" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ15" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CN15" s="81" t="s">
+      <c r="CH15" s="80"/>
+      <c r="CI15" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ15" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CN15" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="CO15" s="81" t="s">
+      <c r="CO15" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CP15" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ15" s="81" t="s">
+      <c r="CP15" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ15" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CR15" s="81"/>
-      <c r="CS15" s="81"/>
-      <c r="CT15" s="81" t="s">
+      <c r="CR15" s="80"/>
+      <c r="CS15" s="80"/>
+      <c r="CT15" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="CU15" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV15" s="81" t="s">
+      <c r="CU15" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV15" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="CW15" s="81" t="s">
+      <c r="CW15" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="CX15" s="81" t="s">
+      <c r="CX15" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="CY15" s="81"/>
-      <c r="CZ15" s="86" t="s">
+      <c r="CY15" s="80"/>
+      <c r="CZ15" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="DA15" s="80" t="s">
+      <c r="DA15" t="s">
         <v>135</v>
       </c>
-      <c r="DB15" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC15" s="81" t="s">
+      <c r="DB15" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC15" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="DD15" s="81"/>
-      <c r="DE15" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF15" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DN15" s="81" t="s">
+      <c r="DD15" s="80"/>
+      <c r="DE15" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF15" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DN15" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DO15" s="81" t="s">
+      <c r="DO15" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="DP15" s="81" t="s">
+      <c r="DP15" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="DQ15" s="81">
+      <c r="DQ15" s="80">
         <v>1765</v>
       </c>
-      <c r="DR15" s="81" t="s">
+      <c r="DR15" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="DS15" s="81" t="s">
+      <c r="DS15" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="DT15" s="81" t="s">
+      <c r="DT15" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="DU15" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DV15" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DW15" s="81" t="s">
+      <c r="DU15" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DV15" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DW15" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="DZ15" s="81" t="s">
+      <c r="DZ15" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="EA15" s="81" t="s">
+      <c r="EA15" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EB15" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EC15" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="ED15" s="81" t="s">
+      <c r="EB15" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC15" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="ED15" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="EE15" s="81" t="s">
+      <c r="EE15" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EF15" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EG15" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EH15" s="81" t="s">
+      <c r="EF15" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EG15" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EH15" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="EI15" s="81" t="s">
+      <c r="EI15" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="EJ15" s="81" t="s">
+      <c r="EJ15" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="EK15" s="81"/>
-      <c r="EL15" s="81" t="s">
+      <c r="EK15" s="80"/>
+      <c r="EL15" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="EM15" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EN15" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EO15" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EP15" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="EQ15" s="81" t="s">
+      <c r="EM15" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EN15" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EO15" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EP15" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ15" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="ER15" s="81" t="s">
+      <c r="ER15" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="ES15" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="ET15" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="EU15" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EV15" s="82" t="s">
+      <c r="ES15" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="ET15" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="EU15" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EV15" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:467" x14ac:dyDescent="0.25">
-      <c r="A16" s="81" t="s">
+      <c r="A16" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="81" t="s">
+      <c r="B16" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="81" t="s">
+      <c r="C16" s="80"/>
+      <c r="D16" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="81" t="s">
+      <c r="E16" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="82"/>
-      <c r="I16" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81" t="s">
+      <c r="F16" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N16" s="80"/>
+      <c r="O16" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="P16" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q16" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AM16" s="81" t="s">
+      <c r="P16" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" s="80"/>
+      <c r="S16" s="80"/>
+      <c r="T16" s="80"/>
+      <c r="U16" s="80"/>
+      <c r="V16" s="80"/>
+      <c r="W16" s="80"/>
+      <c r="X16" s="80"/>
+      <c r="Y16" s="80"/>
+      <c r="Z16" s="80"/>
+      <c r="AM16" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="AN16" s="81" t="s">
+      <c r="AN16" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO16" s="81"/>
-      <c r="AP16" s="81" t="s">
+      <c r="AO16" s="80"/>
+      <c r="AP16" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AQ16" s="81" t="s">
+      <c r="AQ16" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AR16" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS16" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT16" s="82"/>
-      <c r="AU16" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV16" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ16" s="81"/>
-      <c r="BA16" s="81" t="s">
+      <c r="AR16" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS16" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT16" s="81"/>
+      <c r="AU16" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV16" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ16" s="80"/>
+      <c r="BA16" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="BB16" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC16" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD16" s="81"/>
-      <c r="BE16" s="81" t="s">
+      <c r="BB16" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC16" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD16" s="80"/>
+      <c r="BE16" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="BF16" s="81"/>
-      <c r="BG16" s="81"/>
-      <c r="BH16" s="81"/>
-      <c r="BI16" s="81"/>
-      <c r="BJ16" s="81" t="s">
+      <c r="BF16" s="80"/>
+      <c r="BG16" s="80"/>
+      <c r="BH16" s="80"/>
+      <c r="BI16" s="80"/>
+      <c r="BJ16" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="BK16" s="80" t="s">
+      <c r="BK16" t="s">
         <v>61</v>
       </c>
-      <c r="CA16" s="81" t="s">
+      <c r="CA16" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="CB16" s="81" t="s">
+      <c r="CB16" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="CC16" s="81" t="s">
+      <c r="CC16" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="CD16" s="81">
+      <c r="CD16" s="80">
         <v>1790</v>
       </c>
-      <c r="CE16" s="81" t="s">
+      <c r="CE16" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CF16" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG16" s="81" t="s">
+      <c r="CF16" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG16" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CH16" s="81"/>
-      <c r="CI16" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ16" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CN16" s="81" t="s">
+      <c r="CH16" s="80"/>
+      <c r="CI16" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ16" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CN16" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="CO16" s="81" t="s">
+      <c r="CO16" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CP16" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ16" s="81" t="s">
+      <c r="CP16" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ16" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CR16" s="81"/>
-      <c r="CS16" s="81"/>
-      <c r="CT16" s="81" t="s">
+      <c r="CR16" s="80"/>
+      <c r="CS16" s="80"/>
+      <c r="CT16" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="CU16" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV16" s="81" t="s">
+      <c r="CU16" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV16" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="CW16" s="81" t="s">
+      <c r="CW16" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="CX16" s="81" t="s">
+      <c r="CX16" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="CY16" s="81"/>
-      <c r="CZ16" s="86" t="s">
+      <c r="CY16" s="80"/>
+      <c r="CZ16" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="DA16" s="80" t="s">
+      <c r="DA16" t="s">
         <v>135</v>
       </c>
-      <c r="DB16" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC16" s="81" t="s">
+      <c r="DB16" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC16" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="DD16" s="81"/>
-      <c r="DE16" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF16" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DN16" s="81" t="s">
+      <c r="DD16" s="80"/>
+      <c r="DE16" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF16" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DN16" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DO16" s="81" t="s">
+      <c r="DO16" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="DP16" s="81" t="s">
+      <c r="DP16" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="DQ16" s="81">
+      <c r="DQ16" s="80">
         <v>1765</v>
       </c>
-      <c r="DR16" s="81" t="s">
+      <c r="DR16" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="DS16" s="81" t="s">
+      <c r="DS16" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="DT16" s="81" t="s">
+      <c r="DT16" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="DU16" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DV16" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DW16" s="81" t="s">
+      <c r="DU16" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DV16" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DW16" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="DZ16" s="81" t="s">
+      <c r="DZ16" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="EA16" s="81" t="s">
+      <c r="EA16" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EB16" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EC16" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="ED16" s="81" t="s">
+      <c r="EB16" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC16" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="ED16" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="EE16" s="81" t="s">
+      <c r="EE16" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EF16" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EG16" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EH16" s="81" t="s">
+      <c r="EF16" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EG16" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EH16" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="EI16" s="81" t="s">
+      <c r="EI16" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="EJ16" s="81" t="s">
+      <c r="EJ16" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="EK16" s="81"/>
-      <c r="EL16" s="81" t="s">
+      <c r="EK16" s="80"/>
+      <c r="EL16" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="EM16" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EN16" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EO16" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EP16" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="EQ16" s="81" t="s">
+      <c r="EM16" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EN16" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EO16" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EP16" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ16" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="ER16" s="81" t="s">
+      <c r="ER16" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="ES16" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="ET16" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="EU16" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EV16" s="82" t="s">
+      <c r="ES16" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="ET16" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="EU16" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EV16" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="80" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="81" t="s">
+      <c r="B17" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="81"/>
-      <c r="D17" s="81" t="s">
+      <c r="C17" s="80"/>
+      <c r="D17" s="80" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="81" t="s">
+      <c r="E17" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H17" s="82"/>
-      <c r="I17" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N17" s="81"/>
-      <c r="O17" s="81" t="s">
+      <c r="F17" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="81"/>
+      <c r="I17" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N17" s="80"/>
+      <c r="O17" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="P17" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q17" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R17" s="81"/>
-      <c r="S17" s="81"/>
-      <c r="T17" s="81"/>
-      <c r="U17" s="81"/>
-      <c r="V17" s="81"/>
-      <c r="W17" s="81"/>
-      <c r="X17" s="81"/>
-      <c r="Y17" s="81"/>
-      <c r="Z17" s="81"/>
-      <c r="AM17" s="81" t="s">
+      <c r="P17" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q17" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R17" s="80"/>
+      <c r="S17" s="80"/>
+      <c r="T17" s="80"/>
+      <c r="U17" s="80"/>
+      <c r="V17" s="80"/>
+      <c r="W17" s="80"/>
+      <c r="X17" s="80"/>
+      <c r="Y17" s="80"/>
+      <c r="Z17" s="80"/>
+      <c r="AM17" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="AN17" s="81" t="s">
+      <c r="AN17" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO17" s="81"/>
-      <c r="AP17" s="81" t="s">
+      <c r="AO17" s="80"/>
+      <c r="AP17" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AQ17" s="81" t="s">
+      <c r="AQ17" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AR17" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS17" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT17" s="82"/>
-      <c r="AU17" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV17" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ17" s="81"/>
-      <c r="BA17" s="81" t="s">
+      <c r="AR17" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS17" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT17" s="81"/>
+      <c r="AU17" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV17" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ17" s="80"/>
+      <c r="BA17" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="BB17" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC17" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD17" s="81"/>
-      <c r="BE17" s="81" t="s">
+      <c r="BB17" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC17" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD17" s="80"/>
+      <c r="BE17" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="BF17" s="81"/>
-      <c r="BG17" s="81"/>
-      <c r="BH17" s="81"/>
-      <c r="BI17" s="81"/>
-      <c r="BJ17" s="81" t="s">
+      <c r="BF17" s="80"/>
+      <c r="BG17" s="80"/>
+      <c r="BH17" s="80"/>
+      <c r="BI17" s="80"/>
+      <c r="BJ17" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="BK17" s="80" t="s">
+      <c r="BK17" t="s">
         <v>61</v>
       </c>
-      <c r="CA17" s="81" t="s">
+      <c r="CA17" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="CB17" s="81" t="s">
+      <c r="CB17" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="CC17" s="81" t="s">
+      <c r="CC17" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="CD17" s="81">
+      <c r="CD17" s="80">
         <v>1790</v>
       </c>
-      <c r="CE17" s="81" t="s">
+      <c r="CE17" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CF17" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG17" s="81" t="s">
+      <c r="CF17" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG17" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CH17" s="81"/>
-      <c r="CI17" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ17" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CN17" s="81" t="s">
+      <c r="CH17" s="80"/>
+      <c r="CI17" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ17" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CN17" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="CO17" s="81" t="s">
+      <c r="CO17" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CP17" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ17" s="81" t="s">
+      <c r="CP17" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ17" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CR17" s="81"/>
-      <c r="CS17" s="81"/>
-      <c r="CT17" s="81" t="s">
+      <c r="CR17" s="80"/>
+      <c r="CS17" s="80"/>
+      <c r="CT17" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="CU17" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV17" s="81" t="s">
+      <c r="CU17" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV17" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="CW17" s="81" t="s">
+      <c r="CW17" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="CX17" s="81" t="s">
+      <c r="CX17" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="CY17" s="81"/>
-      <c r="CZ17" s="86" t="s">
+      <c r="CY17" s="80"/>
+      <c r="CZ17" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="DA17" s="80" t="s">
+      <c r="DA17" t="s">
         <v>135</v>
       </c>
-      <c r="DB17" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC17" s="81" t="s">
+      <c r="DB17" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC17" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="DD17" s="81"/>
-      <c r="DE17" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF17" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DN17" s="81" t="s">
+      <c r="DD17" s="80"/>
+      <c r="DE17" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF17" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DN17" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DO17" s="81" t="s">
+      <c r="DO17" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="DP17" s="81" t="s">
+      <c r="DP17" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="DQ17" s="81">
+      <c r="DQ17" s="80">
         <v>1765</v>
       </c>
-      <c r="DR17" s="81" t="s">
+      <c r="DR17" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="DS17" s="81" t="s">
+      <c r="DS17" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="DT17" s="81" t="s">
+      <c r="DT17" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="DU17" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DV17" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DW17" s="81" t="s">
+      <c r="DU17" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DV17" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DW17" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="DZ17" s="81" t="s">
+      <c r="DZ17" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="EA17" s="81" t="s">
+      <c r="EA17" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EB17" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EC17" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="ED17" s="81" t="s">
+      <c r="EB17" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC17" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="ED17" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="EE17" s="81" t="s">
+      <c r="EE17" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EF17" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EG17" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EH17" s="81" t="s">
+      <c r="EF17" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EG17" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EH17" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="EI17" s="81" t="s">
+      <c r="EI17" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="EJ17" s="81" t="s">
+      <c r="EJ17" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="EK17" s="81"/>
-      <c r="EL17" s="81" t="s">
+      <c r="EK17" s="80"/>
+      <c r="EL17" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="EM17" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EN17" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EO17" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EP17" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="EQ17" s="81" t="s">
+      <c r="EM17" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EN17" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EO17" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EP17" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ17" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="ER17" s="81" t="s">
+      <c r="ER17" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="ES17" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="ET17" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="EU17" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EV17" s="82" t="s">
+      <c r="ES17" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="ET17" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="EU17" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EV17" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="A18" s="81" t="s">
+      <c r="A18" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="81" t="s">
+      <c r="B18" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81" t="s">
+      <c r="C18" s="80"/>
+      <c r="D18" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="81" t="s">
+      <c r="E18" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" s="82"/>
-      <c r="I18" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N18" s="81"/>
-      <c r="O18" s="81" t="s">
+      <c r="F18" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" s="80"/>
+      <c r="O18" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="P18" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q18" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R18" s="81"/>
-      <c r="S18" s="81"/>
-      <c r="T18" s="81"/>
-      <c r="U18" s="81"/>
-      <c r="V18" s="81"/>
-      <c r="W18" s="81"/>
-      <c r="X18" s="81"/>
-      <c r="Y18" s="81"/>
-      <c r="Z18" s="81"/>
-      <c r="AM18" s="81" t="s">
+      <c r="P18" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q18" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R18" s="80"/>
+      <c r="S18" s="80"/>
+      <c r="T18" s="80"/>
+      <c r="U18" s="80"/>
+      <c r="V18" s="80"/>
+      <c r="W18" s="80"/>
+      <c r="X18" s="80"/>
+      <c r="Y18" s="80"/>
+      <c r="Z18" s="80"/>
+      <c r="AM18" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="AN18" s="81" t="s">
+      <c r="AN18" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO18" s="81"/>
-      <c r="AP18" s="81" t="s">
+      <c r="AO18" s="80"/>
+      <c r="AP18" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AQ18" s="81" t="s">
+      <c r="AQ18" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AR18" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS18" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT18" s="82"/>
-      <c r="AU18" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV18" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ18" s="81"/>
-      <c r="BA18" s="81" t="s">
+      <c r="AR18" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS18" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT18" s="81"/>
+      <c r="AU18" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV18" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ18" s="80"/>
+      <c r="BA18" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="BB18" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC18" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD18" s="81"/>
-      <c r="BE18" s="81" t="s">
+      <c r="BB18" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC18" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD18" s="80"/>
+      <c r="BE18" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="BF18" s="81"/>
-      <c r="BG18" s="81"/>
-      <c r="BH18" s="81"/>
-      <c r="BI18" s="81"/>
-      <c r="BJ18" s="81" t="s">
+      <c r="BF18" s="80"/>
+      <c r="BG18" s="80"/>
+      <c r="BH18" s="80"/>
+      <c r="BI18" s="80"/>
+      <c r="BJ18" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="BK18" s="80" t="s">
+      <c r="BK18" t="s">
         <v>61</v>
       </c>
-      <c r="CA18" s="81" t="s">
+      <c r="CA18" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="CB18" s="81" t="s">
+      <c r="CB18" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="CC18" s="81" t="s">
+      <c r="CC18" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="CD18" s="81">
+      <c r="CD18" s="80">
         <v>1790</v>
       </c>
-      <c r="CE18" s="81" t="s">
+      <c r="CE18" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CF18" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG18" s="81" t="s">
+      <c r="CF18" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG18" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CH18" s="81"/>
-      <c r="CI18" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ18" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CN18" s="81" t="s">
+      <c r="CH18" s="80"/>
+      <c r="CI18" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ18" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CN18" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="CO18" s="81" t="s">
+      <c r="CO18" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CP18" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ18" s="81" t="s">
+      <c r="CP18" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ18" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CR18" s="81"/>
-      <c r="CS18" s="81"/>
-      <c r="CT18" s="81" t="s">
+      <c r="CR18" s="80"/>
+      <c r="CS18" s="80"/>
+      <c r="CT18" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="CU18" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV18" s="81" t="s">
+      <c r="CU18" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV18" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="CW18" s="81" t="s">
+      <c r="CW18" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="CX18" s="81" t="s">
+      <c r="CX18" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="CY18" s="81"/>
-      <c r="CZ18" s="86" t="s">
+      <c r="CY18" s="80"/>
+      <c r="CZ18" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="DA18" s="80" t="s">
+      <c r="DA18" t="s">
         <v>135</v>
       </c>
-      <c r="DB18" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC18" s="81" t="s">
+      <c r="DB18" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC18" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="DD18" s="81"/>
-      <c r="DE18" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF18" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DN18" s="81" t="s">
+      <c r="DD18" s="80"/>
+      <c r="DE18" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF18" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DN18" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DO18" s="81" t="s">
+      <c r="DO18" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="DP18" s="81" t="s">
+      <c r="DP18" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="DQ18" s="81">
+      <c r="DQ18" s="80">
         <v>1765</v>
       </c>
-      <c r="DR18" s="81" t="s">
+      <c r="DR18" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="DS18" s="81" t="s">
+      <c r="DS18" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="DT18" s="81" t="s">
+      <c r="DT18" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="DU18" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DV18" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DW18" s="81" t="s">
+      <c r="DU18" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DV18" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DW18" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="DZ18" s="81" t="s">
+      <c r="DZ18" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="EA18" s="81" t="s">
+      <c r="EA18" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EB18" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EC18" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="ED18" s="81" t="s">
+      <c r="EB18" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC18" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="ED18" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="EE18" s="81" t="s">
+      <c r="EE18" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EF18" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EG18" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EH18" s="81" t="s">
+      <c r="EF18" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EG18" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EH18" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="EI18" s="81" t="s">
+      <c r="EI18" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="EJ18" s="81" t="s">
+      <c r="EJ18" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="EK18" s="81"/>
-      <c r="EL18" s="81" t="s">
+      <c r="EK18" s="80"/>
+      <c r="EL18" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="EM18" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EN18" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EO18" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EP18" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="EQ18" s="81" t="s">
+      <c r="EM18" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EN18" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EO18" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EP18" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ18" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="ER18" s="81" t="s">
+      <c r="ER18" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="ES18" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="ET18" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="EU18" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EV18" s="82" t="s">
+      <c r="ES18" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="ET18" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="EU18" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EV18" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="A19" s="81" t="s">
+      <c r="A19" s="80" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="81" t="s">
+      <c r="B19" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="81"/>
-      <c r="D19" s="81" t="s">
+      <c r="C19" s="80"/>
+      <c r="D19" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="81" t="s">
+      <c r="E19" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H19" s="82"/>
-      <c r="I19" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N19" s="81"/>
-      <c r="O19" s="81" t="s">
+      <c r="F19" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N19" s="80"/>
+      <c r="O19" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="P19" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q19" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R19" s="81"/>
-      <c r="S19" s="81"/>
-      <c r="T19" s="81"/>
-      <c r="U19" s="81"/>
-      <c r="V19" s="81"/>
-      <c r="W19" s="81"/>
-      <c r="X19" s="81"/>
-      <c r="Y19" s="81"/>
-      <c r="Z19" s="81"/>
-      <c r="AM19" s="81" t="s">
+      <c r="P19" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R19" s="80"/>
+      <c r="S19" s="80"/>
+      <c r="T19" s="80"/>
+      <c r="U19" s="80"/>
+      <c r="V19" s="80"/>
+      <c r="W19" s="80"/>
+      <c r="X19" s="80"/>
+      <c r="Y19" s="80"/>
+      <c r="Z19" s="80"/>
+      <c r="AM19" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="AN19" s="81" t="s">
+      <c r="AN19" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO19" s="81"/>
-      <c r="AP19" s="81" t="s">
+      <c r="AO19" s="80"/>
+      <c r="AP19" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AQ19" s="81" t="s">
+      <c r="AQ19" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AR19" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS19" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT19" s="82"/>
-      <c r="AU19" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV19" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ19" s="81"/>
-      <c r="BA19" s="81" t="s">
+      <c r="AR19" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS19" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT19" s="81"/>
+      <c r="AU19" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV19" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ19" s="80"/>
+      <c r="BA19" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="BB19" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC19" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD19" s="81"/>
-      <c r="BE19" s="81" t="s">
+      <c r="BB19" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC19" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD19" s="80"/>
+      <c r="BE19" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="BF19" s="81"/>
-      <c r="BG19" s="81"/>
-      <c r="BH19" s="81"/>
-      <c r="BI19" s="81"/>
-      <c r="BJ19" s="81" t="s">
+      <c r="BF19" s="80"/>
+      <c r="BG19" s="80"/>
+      <c r="BH19" s="80"/>
+      <c r="BI19" s="80"/>
+      <c r="BJ19" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="BK19" s="80" t="s">
+      <c r="BK19" t="s">
         <v>61</v>
       </c>
-      <c r="CA19" s="81" t="s">
+      <c r="CA19" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="CB19" s="81" t="s">
+      <c r="CB19" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="CC19" s="81" t="s">
+      <c r="CC19" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="CD19" s="81">
+      <c r="CD19" s="80">
         <v>1790</v>
       </c>
-      <c r="CE19" s="81" t="s">
+      <c r="CE19" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CF19" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG19" s="81" t="s">
+      <c r="CF19" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG19" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CH19" s="81"/>
-      <c r="CI19" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ19" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CN19" s="81" t="s">
+      <c r="CH19" s="80"/>
+      <c r="CI19" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ19" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CN19" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="CO19" s="81" t="s">
+      <c r="CO19" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CP19" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ19" s="81" t="s">
+      <c r="CP19" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ19" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CR19" s="81"/>
-      <c r="CS19" s="81"/>
-      <c r="CT19" s="81" t="s">
+      <c r="CR19" s="80"/>
+      <c r="CS19" s="80"/>
+      <c r="CT19" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="CU19" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV19" s="81" t="s">
+      <c r="CU19" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV19" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="CW19" s="81" t="s">
+      <c r="CW19" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="CX19" s="81" t="s">
+      <c r="CX19" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="CY19" s="81"/>
-      <c r="CZ19" s="86" t="s">
+      <c r="CY19" s="80"/>
+      <c r="CZ19" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="DA19" s="80" t="s">
+      <c r="DA19" t="s">
         <v>135</v>
       </c>
-      <c r="DB19" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC19" s="81" t="s">
+      <c r="DB19" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC19" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="DD19" s="81"/>
-      <c r="DE19" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF19" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DN19" s="81" t="s">
+      <c r="DD19" s="80"/>
+      <c r="DE19" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF19" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DN19" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DO19" s="81" t="s">
+      <c r="DO19" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="DP19" s="81" t="s">
+      <c r="DP19" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="DQ19" s="81">
+      <c r="DQ19" s="80">
         <v>1765</v>
       </c>
-      <c r="DR19" s="81" t="s">
+      <c r="DR19" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="DS19" s="81" t="s">
+      <c r="DS19" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="DT19" s="81" t="s">
+      <c r="DT19" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="DU19" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DV19" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DW19" s="81" t="s">
+      <c r="DU19" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DV19" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DW19" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="DZ19" s="81" t="s">
+      <c r="DZ19" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="EA19" s="81" t="s">
+      <c r="EA19" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EB19" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EC19" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="ED19" s="81" t="s">
+      <c r="EB19" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC19" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="ED19" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="EE19" s="81" t="s">
+      <c r="EE19" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EF19" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EG19" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EH19" s="81" t="s">
+      <c r="EF19" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EG19" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EH19" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="EI19" s="81" t="s">
+      <c r="EI19" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="EJ19" s="81" t="s">
+      <c r="EJ19" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="EK19" s="81"/>
-      <c r="EL19" s="81" t="s">
+      <c r="EK19" s="80"/>
+      <c r="EL19" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="EM19" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EN19" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EO19" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EP19" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="EQ19" s="81" t="s">
+      <c r="EM19" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EN19" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EO19" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EP19" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ19" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="ER19" s="81" t="s">
+      <c r="ER19" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="ES19" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="ET19" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="EU19" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EV19" s="82" t="s">
+      <c r="ES19" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="ET19" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="EU19" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EV19" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="81" t="s">
+      <c r="B20" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="81"/>
-      <c r="D20" s="81" t="s">
+      <c r="C20" s="80"/>
+      <c r="D20" s="80" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="81" t="s">
+      <c r="E20" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H20" s="82"/>
-      <c r="I20" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N20" s="81"/>
-      <c r="O20" s="81" t="s">
+      <c r="F20" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="81"/>
+      <c r="I20" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N20" s="80"/>
+      <c r="O20" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="P20" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q20" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R20" s="81"/>
-      <c r="S20" s="81"/>
-      <c r="T20" s="81"/>
-      <c r="U20" s="81"/>
-      <c r="V20" s="81"/>
-      <c r="W20" s="81"/>
-      <c r="X20" s="81" t="s">
+      <c r="P20" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R20" s="80"/>
+      <c r="S20" s="80"/>
+      <c r="T20" s="80"/>
+      <c r="U20" s="80"/>
+      <c r="V20" s="80"/>
+      <c r="W20" s="80"/>
+      <c r="X20" s="80" t="s">
         <v>117</v>
       </c>
-      <c r="Y20" s="80" t="s">
+      <c r="Y20" t="s">
         <v>118</v>
       </c>
-      <c r="AM20" s="81" t="s">
+      <c r="AM20" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="AN20" s="81" t="s">
+      <c r="AN20" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO20" s="81"/>
-      <c r="AP20" s="81" t="s">
+      <c r="AO20" s="80"/>
+      <c r="AP20" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AQ20" s="81" t="s">
+      <c r="AQ20" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AR20" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS20" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT20" s="82"/>
-      <c r="AU20" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV20" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ20" s="81"/>
-      <c r="BA20" s="81" t="s">
+      <c r="AR20" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS20" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT20" s="81"/>
+      <c r="AU20" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV20" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ20" s="80"/>
+      <c r="BA20" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="BB20" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC20" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD20" s="81"/>
-      <c r="BE20" s="81" t="s">
+      <c r="BB20" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC20" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD20" s="80"/>
+      <c r="BE20" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="BF20" s="81"/>
-      <c r="BG20" s="81"/>
-      <c r="BH20" s="81"/>
-      <c r="BI20" s="81"/>
-      <c r="BJ20" s="81" t="s">
+      <c r="BF20" s="80"/>
+      <c r="BG20" s="80"/>
+      <c r="BH20" s="80"/>
+      <c r="BI20" s="80"/>
+      <c r="BJ20" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="BK20" s="80" t="s">
+      <c r="BK20" t="s">
         <v>61</v>
       </c>
-      <c r="CA20" s="81" t="s">
+      <c r="CA20" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="CB20" s="81" t="s">
+      <c r="CB20" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="CC20" s="81" t="s">
+      <c r="CC20" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="CD20" s="81">
+      <c r="CD20" s="80">
         <v>1790</v>
       </c>
-      <c r="CE20" s="81" t="s">
+      <c r="CE20" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CF20" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG20" s="81" t="s">
+      <c r="CF20" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG20" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CH20" s="81"/>
-      <c r="CI20" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ20" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CN20" s="81" t="s">
+      <c r="CH20" s="80"/>
+      <c r="CI20" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ20" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CN20" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="CO20" s="81" t="s">
+      <c r="CO20" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CP20" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ20" s="81" t="s">
+      <c r="CP20" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ20" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CR20" s="81"/>
-      <c r="CS20" s="81"/>
-      <c r="CT20" s="81" t="s">
+      <c r="CR20" s="80"/>
+      <c r="CS20" s="80"/>
+      <c r="CT20" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="CU20" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV20" s="81" t="s">
+      <c r="CU20" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV20" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="CW20" s="81" t="s">
+      <c r="CW20" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="CX20" s="81" t="s">
+      <c r="CX20" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="CY20" s="81"/>
-      <c r="CZ20" s="86" t="s">
+      <c r="CY20" s="80"/>
+      <c r="CZ20" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="DA20" s="80" t="s">
+      <c r="DA20" t="s">
         <v>135</v>
       </c>
-      <c r="DB20" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC20" s="81" t="s">
+      <c r="DB20" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC20" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="DD20" s="81"/>
-      <c r="DE20" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF20" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DN20" s="81" t="s">
+      <c r="DD20" s="80"/>
+      <c r="DE20" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF20" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DN20" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DO20" s="81" t="s">
+      <c r="DO20" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="DP20" s="81" t="s">
+      <c r="DP20" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="DQ20" s="81">
+      <c r="DQ20" s="80">
         <v>1765</v>
       </c>
-      <c r="DR20" s="81" t="s">
+      <c r="DR20" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="DS20" s="81" t="s">
+      <c r="DS20" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="DT20" s="81" t="s">
+      <c r="DT20" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="DU20" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DV20" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DW20" s="81" t="s">
+      <c r="DU20" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DV20" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DW20" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="DZ20" s="81" t="s">
+      <c r="DZ20" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="EA20" s="81" t="s">
+      <c r="EA20" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EB20" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EC20" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="ED20" s="81" t="s">
+      <c r="EB20" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC20" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="ED20" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="EE20" s="81" t="s">
+      <c r="EE20" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EF20" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EG20" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EH20" s="81" t="s">
+      <c r="EF20" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EG20" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EH20" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="EI20" s="81" t="s">
+      <c r="EI20" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="EJ20" s="81" t="s">
+      <c r="EJ20" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="EK20" s="81"/>
-      <c r="EL20" s="81" t="s">
+      <c r="EK20" s="80"/>
+      <c r="EL20" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="EM20" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EN20" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EO20" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EP20" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="EQ20" s="81" t="s">
+      <c r="EM20" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EN20" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EO20" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EP20" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ20" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="ER20" s="81" t="s">
+      <c r="ER20" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="ES20" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="ET20" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="EU20" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EV20" s="82" t="s">
+      <c r="ES20" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="ET20" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="EU20" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EV20" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="A21" s="81" t="s">
+      <c r="A21" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="81" t="s">
+      <c r="B21" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="81"/>
-      <c r="D21" s="81" t="s">
+      <c r="C21" s="80"/>
+      <c r="D21" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="E21" s="81" t="s">
+      <c r="E21" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H21" s="82"/>
-      <c r="I21" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N21" s="81" t="s">
+      <c r="F21" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="81"/>
+      <c r="I21" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="O21" s="81" t="s">
+      <c r="O21" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="P21" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q21" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R21" s="81"/>
-      <c r="S21" s="81"/>
-      <c r="T21" s="81"/>
-      <c r="U21" s="81"/>
-      <c r="V21" s="81"/>
-      <c r="W21" s="81"/>
-      <c r="X21" s="81" t="s">
+      <c r="P21" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R21" s="80"/>
+      <c r="S21" s="80"/>
+      <c r="T21" s="80"/>
+      <c r="U21" s="80"/>
+      <c r="V21" s="80"/>
+      <c r="W21" s="80"/>
+      <c r="X21" s="80" t="s">
         <v>119</v>
       </c>
-      <c r="Y21" s="80" t="s">
+      <c r="Y21" t="s">
         <v>120</v>
       </c>
-      <c r="AM21" s="81" t="s">
+      <c r="AM21" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="AN21" s="81" t="s">
+      <c r="AN21" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO21" s="81"/>
-      <c r="AP21" s="81" t="s">
+      <c r="AO21" s="80"/>
+      <c r="AP21" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AQ21" s="81" t="s">
+      <c r="AQ21" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AR21" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS21" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT21" s="82"/>
-      <c r="AU21" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV21" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ21" s="81"/>
-      <c r="BA21" s="81" t="s">
+      <c r="AR21" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS21" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT21" s="81"/>
+      <c r="AU21" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV21" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ21" s="80"/>
+      <c r="BA21" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="BB21" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC21" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD21" s="81"/>
-      <c r="BE21" s="81" t="s">
+      <c r="BB21" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC21" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD21" s="80"/>
+      <c r="BE21" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="BF21" s="81"/>
-      <c r="BG21" s="81"/>
-      <c r="BH21" s="81"/>
-      <c r="BI21" s="81"/>
-      <c r="BJ21" s="81" t="s">
+      <c r="BF21" s="80"/>
+      <c r="BG21" s="80"/>
+      <c r="BH21" s="80"/>
+      <c r="BI21" s="80"/>
+      <c r="BJ21" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="BK21" s="80" t="s">
+      <c r="BK21" t="s">
         <v>61</v>
       </c>
-      <c r="CA21" s="81" t="s">
+      <c r="CA21" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="CB21" s="81" t="s">
+      <c r="CB21" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="CC21" s="81" t="s">
+      <c r="CC21" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="CD21" s="81">
+      <c r="CD21" s="80">
         <v>1790</v>
       </c>
-      <c r="CE21" s="81" t="s">
+      <c r="CE21" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CF21" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG21" s="81" t="s">
+      <c r="CF21" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG21" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CH21" s="81"/>
-      <c r="CI21" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ21" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CN21" s="81" t="s">
+      <c r="CH21" s="80"/>
+      <c r="CI21" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ21" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CN21" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="CO21" s="81" t="s">
+      <c r="CO21" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CP21" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ21" s="81" t="s">
+      <c r="CP21" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ21" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CR21" s="81"/>
-      <c r="CS21" s="81"/>
-      <c r="CT21" s="81" t="s">
+      <c r="CR21" s="80"/>
+      <c r="CS21" s="80"/>
+      <c r="CT21" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="CU21" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV21" s="81" t="s">
+      <c r="CU21" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV21" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="CW21" s="81" t="s">
+      <c r="CW21" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="CX21" s="81" t="s">
+      <c r="CX21" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="CY21" s="81"/>
-      <c r="CZ21" s="86" t="s">
+      <c r="CY21" s="80"/>
+      <c r="CZ21" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="DA21" s="80" t="s">
+      <c r="DA21" t="s">
         <v>135</v>
       </c>
-      <c r="DB21" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC21" s="81" t="s">
+      <c r="DB21" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC21" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="DD21" s="81"/>
-      <c r="DE21" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF21" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DN21" s="81" t="s">
+      <c r="DD21" s="80"/>
+      <c r="DE21" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF21" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DN21" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DO21" s="81" t="s">
+      <c r="DO21" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="DP21" s="81" t="s">
+      <c r="DP21" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="DQ21" s="81">
+      <c r="DQ21" s="80">
         <v>1765</v>
       </c>
-      <c r="DR21" s="81" t="s">
+      <c r="DR21" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="DS21" s="81" t="s">
+      <c r="DS21" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="DT21" s="81" t="s">
+      <c r="DT21" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="DU21" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DV21" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DW21" s="81" t="s">
+      <c r="DU21" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DV21" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DW21" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="DZ21" s="81" t="s">
+      <c r="DZ21" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="EA21" s="81" t="s">
+      <c r="EA21" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EB21" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EC21" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="ED21" s="81" t="s">
+      <c r="EB21" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC21" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="ED21" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="EE21" s="81" t="s">
+      <c r="EE21" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EF21" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EG21" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EH21" s="81" t="s">
+      <c r="EF21" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EG21" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EH21" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="EI21" s="81" t="s">
+      <c r="EI21" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="EJ21" s="81" t="s">
+      <c r="EJ21" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="EK21" s="81"/>
-      <c r="EL21" s="81" t="s">
+      <c r="EK21" s="80"/>
+      <c r="EL21" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="EM21" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EN21" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EO21" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EP21" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="EQ21" s="81" t="s">
+      <c r="EM21" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EN21" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EO21" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EP21" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ21" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="ER21" s="81" t="s">
+      <c r="ER21" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="ES21" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="ET21" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="EU21" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EV21" s="82" t="s">
+      <c r="ES21" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="ET21" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="EU21" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EV21" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="A22" s="81" t="s">
+      <c r="A22" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="81" t="s">
+      <c r="B22" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="81"/>
-      <c r="D22" s="81" t="s">
+      <c r="C22" s="80"/>
+      <c r="D22" s="80" t="s">
         <v>83</v>
       </c>
-      <c r="E22" s="81" t="s">
+      <c r="E22" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F22" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G22" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" s="82"/>
-      <c r="I22" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J22" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N22" s="81"/>
-      <c r="O22" s="81" t="s">
+      <c r="F22" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="81"/>
+      <c r="I22" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N22" s="80"/>
+      <c r="O22" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="P22" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q22" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R22" s="81"/>
-      <c r="S22" s="81"/>
-      <c r="T22" s="81"/>
-      <c r="U22" s="81"/>
-      <c r="V22" s="81"/>
-      <c r="W22" s="81"/>
-      <c r="X22" s="81"/>
-      <c r="Y22" s="81"/>
-      <c r="Z22" s="81"/>
-      <c r="AM22" s="81" t="s">
+      <c r="P22" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q22" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R22" s="80"/>
+      <c r="S22" s="80"/>
+      <c r="T22" s="80"/>
+      <c r="U22" s="80"/>
+      <c r="V22" s="80"/>
+      <c r="W22" s="80"/>
+      <c r="X22" s="80"/>
+      <c r="Y22" s="80"/>
+      <c r="Z22" s="80"/>
+      <c r="AM22" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="AN22" s="81" t="s">
+      <c r="AN22" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO22" s="81"/>
-      <c r="AP22" s="81" t="s">
+      <c r="AO22" s="80"/>
+      <c r="AP22" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AQ22" s="81" t="s">
+      <c r="AQ22" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AR22" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS22" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT22" s="82"/>
-      <c r="AU22" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV22" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ22" s="81"/>
-      <c r="BA22" s="81" t="s">
+      <c r="AR22" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS22" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT22" s="81"/>
+      <c r="AU22" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV22" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ22" s="80"/>
+      <c r="BA22" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="BB22" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC22" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD22" s="81"/>
-      <c r="BE22" s="81" t="s">
+      <c r="BB22" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC22" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD22" s="80"/>
+      <c r="BE22" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="BF22" s="81"/>
-      <c r="BG22" s="81"/>
-      <c r="BH22" s="81"/>
-      <c r="BI22" s="81"/>
-      <c r="BJ22" s="81" t="s">
+      <c r="BF22" s="80"/>
+      <c r="BG22" s="80"/>
+      <c r="BH22" s="80"/>
+      <c r="BI22" s="80"/>
+      <c r="BJ22" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="BK22" s="80" t="s">
+      <c r="BK22" t="s">
         <v>61</v>
       </c>
-      <c r="CA22" s="81" t="s">
+      <c r="CA22" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="CB22" s="81" t="s">
+      <c r="CB22" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="CC22" s="81" t="s">
+      <c r="CC22" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="CD22" s="81">
+      <c r="CD22" s="80">
         <v>1790</v>
       </c>
-      <c r="CE22" s="81" t="s">
+      <c r="CE22" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CF22" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG22" s="81" t="s">
+      <c r="CF22" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG22" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CH22" s="81"/>
-      <c r="CI22" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ22" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CN22" s="81" t="s">
+      <c r="CH22" s="80"/>
+      <c r="CI22" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ22" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CN22" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="CO22" s="81" t="s">
+      <c r="CO22" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CP22" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ22" s="81" t="s">
+      <c r="CP22" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ22" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CR22" s="81"/>
-      <c r="CS22" s="81"/>
-      <c r="CT22" s="81" t="s">
+      <c r="CR22" s="80"/>
+      <c r="CS22" s="80"/>
+      <c r="CT22" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="CU22" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV22" s="81" t="s">
+      <c r="CU22" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV22" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="CW22" s="81" t="s">
+      <c r="CW22" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="CX22" s="81" t="s">
+      <c r="CX22" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="CY22" s="81"/>
-      <c r="CZ22" s="86" t="s">
+      <c r="CY22" s="80"/>
+      <c r="CZ22" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="DA22" s="80" t="s">
+      <c r="DA22" t="s">
         <v>135</v>
       </c>
-      <c r="DB22" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC22" s="81" t="s">
+      <c r="DB22" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC22" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="DD22" s="81"/>
-      <c r="DE22" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF22" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DN22" s="81" t="s">
+      <c r="DD22" s="80"/>
+      <c r="DE22" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF22" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DN22" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DO22" s="81" t="s">
+      <c r="DO22" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="DP22" s="81" t="s">
+      <c r="DP22" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="DQ22" s="81">
+      <c r="DQ22" s="80">
         <v>1765</v>
       </c>
-      <c r="DR22" s="81" t="s">
+      <c r="DR22" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="DS22" s="81" t="s">
+      <c r="DS22" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="DT22" s="81" t="s">
+      <c r="DT22" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="DU22" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DV22" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DW22" s="81" t="s">
+      <c r="DU22" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DV22" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DW22" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="DZ22" s="81" t="s">
+      <c r="DZ22" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="EA22" s="81" t="s">
+      <c r="EA22" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EB22" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EC22" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="ED22" s="81" t="s">
+      <c r="EB22" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC22" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="ED22" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="EE22" s="81" t="s">
+      <c r="EE22" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EF22" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EG22" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EH22" s="81" t="s">
+      <c r="EF22" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EG22" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EH22" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="EI22" s="81" t="s">
+      <c r="EI22" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="EJ22" s="81" t="s">
+      <c r="EJ22" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="EK22" s="81"/>
-      <c r="EL22" s="81" t="s">
+      <c r="EK22" s="80"/>
+      <c r="EL22" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="EM22" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EN22" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EO22" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EP22" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="EQ22" s="81" t="s">
+      <c r="EM22" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EN22" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EO22" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EP22" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ22" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="ER22" s="81" t="s">
+      <c r="ER22" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="ES22" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="ET22" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="EU22" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EV22" s="82" t="s">
+      <c r="ES22" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="ET22" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="EU22" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EV22" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="A23" s="81" t="s">
+      <c r="A23" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="81" t="s">
+      <c r="B23" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="81"/>
-      <c r="D23" s="81" t="s">
+      <c r="C23" s="80"/>
+      <c r="D23" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="81" t="s">
+      <c r="E23" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F23" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H23" s="82"/>
-      <c r="I23" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N23" s="81" t="s">
+      <c r="F23" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="81"/>
+      <c r="I23" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N23" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="O23" s="81" t="s">
+      <c r="O23" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="P23" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q23" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R23" s="81"/>
-      <c r="S23" s="81"/>
-      <c r="T23" s="81"/>
-      <c r="U23" s="81"/>
-      <c r="V23" s="81"/>
-      <c r="W23" s="81"/>
-      <c r="X23" s="81"/>
-      <c r="Y23" s="81"/>
-      <c r="Z23" s="81"/>
-      <c r="AM23" s="81" t="s">
+      <c r="P23" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q23" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="R23" s="80"/>
+      <c r="S23" s="80"/>
+      <c r="T23" s="80"/>
+      <c r="U23" s="80"/>
+      <c r="V23" s="80"/>
+      <c r="W23" s="80"/>
+      <c r="X23" s="80"/>
+      <c r="Y23" s="80"/>
+      <c r="Z23" s="80"/>
+      <c r="AM23" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="AN23" s="81" t="s">
+      <c r="AN23" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="AO23" s="81"/>
-      <c r="AP23" s="81" t="s">
+      <c r="AO23" s="80"/>
+      <c r="AP23" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AQ23" s="81" t="s">
+      <c r="AQ23" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AR23" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS23" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT23" s="82"/>
-      <c r="AU23" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV23" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ23" s="81"/>
-      <c r="BA23" s="81" t="s">
+      <c r="AR23" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS23" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT23" s="81"/>
+      <c r="AU23" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV23" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ23" s="80"/>
+      <c r="BA23" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="BB23" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="BC23" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD23" s="81"/>
-      <c r="BE23" s="81" t="s">
+      <c r="BB23" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC23" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD23" s="80"/>
+      <c r="BE23" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="BF23" s="81"/>
-      <c r="BG23" s="81"/>
-      <c r="BH23" s="81"/>
-      <c r="BI23" s="81"/>
-      <c r="BJ23" s="81" t="s">
+      <c r="BF23" s="80"/>
+      <c r="BG23" s="80"/>
+      <c r="BH23" s="80"/>
+      <c r="BI23" s="80"/>
+      <c r="BJ23" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="BK23" s="80" t="s">
+      <c r="BK23" t="s">
         <v>61</v>
       </c>
-      <c r="CA23" s="81" t="s">
+      <c r="CA23" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="CB23" s="81" t="s">
+      <c r="CB23" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="CC23" s="81" t="s">
+      <c r="CC23" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="CD23" s="81">
+      <c r="CD23" s="80">
         <v>1790</v>
       </c>
-      <c r="CE23" s="81" t="s">
+      <c r="CE23" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CF23" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG23" s="81" t="s">
+      <c r="CF23" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG23" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CH23" s="81"/>
-      <c r="CI23" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ23" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CN23" s="81" t="s">
+      <c r="CH23" s="80"/>
+      <c r="CI23" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ23" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CN23" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="CO23" s="81" t="s">
+      <c r="CO23" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CP23" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ23" s="81" t="s">
+      <c r="CP23" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ23" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CR23" s="81"/>
-      <c r="CS23" s="81"/>
-      <c r="CT23" s="81" t="s">
+      <c r="CR23" s="80"/>
+      <c r="CS23" s="80"/>
+      <c r="CT23" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="CU23" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CV23" s="81" t="s">
+      <c r="CU23" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CV23" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="CW23" s="81" t="s">
+      <c r="CW23" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="CX23" s="81" t="s">
+      <c r="CX23" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="CY23" s="81"/>
-      <c r="CZ23" s="86" t="s">
+      <c r="CY23" s="80"/>
+      <c r="CZ23" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="DA23" s="80" t="s">
+      <c r="DA23" t="s">
         <v>135</v>
       </c>
-      <c r="DB23" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC23" s="81" t="s">
+      <c r="DB23" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC23" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="DD23" s="81"/>
-      <c r="DE23" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF23" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DN23" s="81" t="s">
+      <c r="DD23" s="80"/>
+      <c r="DE23" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF23" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DN23" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DO23" s="81" t="s">
+      <c r="DO23" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="DP23" s="81" t="s">
+      <c r="DP23" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="DQ23" s="81">
+      <c r="DQ23" s="80">
         <v>1765</v>
       </c>
-      <c r="DR23" s="81" t="s">
+      <c r="DR23" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="DS23" s="81" t="s">
+      <c r="DS23" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="DT23" s="81" t="s">
+      <c r="DT23" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="DU23" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DV23" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DW23" s="81" t="s">
+      <c r="DU23" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DV23" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DW23" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="DZ23" s="81" t="s">
+      <c r="DZ23" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="EA23" s="81" t="s">
+      <c r="EA23" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EB23" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EC23" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="ED23" s="81" t="s">
+      <c r="EB23" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC23" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="ED23" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="EE23" s="81" t="s">
+      <c r="EE23" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EF23" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EG23" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EH23" s="81" t="s">
+      <c r="EF23" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EG23" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EH23" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="EI23" s="81" t="s">
+      <c r="EI23" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="EJ23" s="81" t="s">
+      <c r="EJ23" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="EK23" s="81"/>
-      <c r="EL23" s="81" t="s">
+      <c r="EK23" s="80"/>
+      <c r="EL23" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="EM23" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EN23" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EO23" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EP23" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="EQ23" s="81" t="s">
+      <c r="EM23" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EN23" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EO23" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EP23" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ23" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="ER23" s="81" t="s">
+      <c r="ER23" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="ES23" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="ET23" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="EU23" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EV23" s="82" t="s">
+      <c r="ES23" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="ET23" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="EU23" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EV23" s="81" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:152" s="85" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:152" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="A25" s="82" t="s">
+      <c r="A25" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="B25" s="82" t="s">
+      <c r="B25" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="82"/>
-      <c r="D25" s="82" t="s">
+      <c r="C25" s="81"/>
+      <c r="D25" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="82" t="s">
+      <c r="E25" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="F25" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" s="82"/>
-      <c r="I25" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J25" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="K25" s="81" t="s">
+      <c r="F25" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="81"/>
+      <c r="I25" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="L25" s="81" t="s">
+      <c r="L25" s="80" t="s">
         <v>142</v>
       </c>
-      <c r="M25" s="80" t="s">
+      <c r="M25" t="s">
         <v>140</v>
       </c>
-      <c r="N25" s="82" t="s">
+      <c r="N25" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="O25" s="82" t="s">
+      <c r="O25" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="P25" s="82" t="s">
+      <c r="P25" s="81" t="s">
         <v>123</v>
       </c>
-      <c r="Q25" s="82" t="s">
+      <c r="Q25" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="R25" s="82"/>
-      <c r="S25" s="82"/>
-      <c r="T25" s="82"/>
-      <c r="U25" s="82"/>
-      <c r="V25" s="82"/>
-      <c r="W25" s="82"/>
-      <c r="X25" s="82"/>
-      <c r="Y25" s="81"/>
-      <c r="Z25" s="81"/>
-      <c r="AM25" s="81" t="s">
+      <c r="R25" s="81"/>
+      <c r="S25" s="81"/>
+      <c r="T25" s="81"/>
+      <c r="U25" s="81"/>
+      <c r="V25" s="81"/>
+      <c r="W25" s="81"/>
+      <c r="X25" s="81"/>
+      <c r="Y25" s="80"/>
+      <c r="Z25" s="80"/>
+      <c r="AM25" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="AN25" s="81" t="s">
+      <c r="AN25" s="80" t="s">
         <v>56</v>
       </c>
-      <c r="AO25" s="81"/>
-      <c r="AP25" s="81" t="s">
+      <c r="AO25" s="80"/>
+      <c r="AP25" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="AQ25" s="81" t="s">
+      <c r="AQ25" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AR25" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="AS25" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT25" s="82"/>
-      <c r="AU25" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV25" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="AZ25" s="81"/>
-      <c r="BA25" s="81"/>
-      <c r="BB25" s="81"/>
-      <c r="BC25" s="81"/>
-      <c r="BD25" s="81"/>
-      <c r="BE25" s="81" t="s">
+      <c r="AR25" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS25" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT25" s="81"/>
+      <c r="AU25" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV25" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ25" s="80"/>
+      <c r="BA25" s="80"/>
+      <c r="BB25" s="80"/>
+      <c r="BC25" s="80"/>
+      <c r="BD25" s="80"/>
+      <c r="BE25" s="80" t="s">
         <v>139</v>
       </c>
-      <c r="BF25" s="81" t="s">
+      <c r="BF25" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="BG25" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="BH25" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="BI25" s="82"/>
-      <c r="BJ25" s="81" t="s">
+      <c r="BG25" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH25" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="BI25" s="81"/>
+      <c r="BJ25" s="80" t="s">
         <v>137</v>
       </c>
-      <c r="BK25" s="81" t="s">
+      <c r="BK25" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="BL25" s="81"/>
-      <c r="BM25" s="80" t="s">
+      <c r="BL25" s="80"/>
+      <c r="BM25" t="s">
         <v>138</v>
       </c>
-      <c r="BN25" s="81" t="s">
+      <c r="BN25" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="BO25" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="BP25" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="BQ25" s="82"/>
-      <c r="BR25" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="BS25" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CA25" s="81" t="s">
+      <c r="BO25" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP25" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="BQ25" s="81"/>
+      <c r="BR25" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS25" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CA25" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="CB25" s="81" t="s">
+      <c r="CB25" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="CC25" s="81" t="s">
+      <c r="CC25" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="CD25" s="81" t="s">
+      <c r="CD25" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="CE25" s="81" t="s">
+      <c r="CE25" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CF25" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG25" s="81" t="s">
+      <c r="CF25" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG25" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CH25" s="81"/>
-      <c r="CI25" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ25" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="CN25" s="81" t="s">
+      <c r="CH25" s="80"/>
+      <c r="CI25" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ25" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="CN25" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="CO25" s="81" t="s">
+      <c r="CO25" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="CP25" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="CQ25" s="81" t="s">
+      <c r="CP25" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ25" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="CR25" s="81"/>
-      <c r="CS25" s="81"/>
-      <c r="CT25" s="81"/>
-      <c r="CU25" s="81"/>
-      <c r="CV25" s="81"/>
-      <c r="CW25" s="81" t="s">
+      <c r="CR25" s="80"/>
+      <c r="CS25" s="80"/>
+      <c r="CT25" s="80"/>
+      <c r="CU25" s="80"/>
+      <c r="CV25" s="80"/>
+      <c r="CW25" s="80" t="s">
         <v>109</v>
       </c>
-      <c r="CX25" s="81" t="s">
+      <c r="CX25" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="CY25" s="81"/>
-      <c r="CZ25" s="80" t="s">
+      <c r="CY25" s="80"/>
+      <c r="CZ25" t="s">
         <v>43</v>
       </c>
-      <c r="DA25" s="80" t="s">
+      <c r="DA25" t="s">
         <v>135</v>
       </c>
-      <c r="DB25" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC25" s="81" t="s">
+      <c r="DB25" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="DC25" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="DD25" s="81"/>
-      <c r="DE25" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DF25" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DN25" s="81" t="s">
+      <c r="DD25" s="80"/>
+      <c r="DE25" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DF25" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DN25" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DO25" s="81" t="s">
+      <c r="DO25" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="DP25" s="81" t="s">
+      <c r="DP25" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="DQ25" s="81">
+      <c r="DQ25" s="80">
         <v>1765</v>
       </c>
-      <c r="DR25" s="81" t="s">
+      <c r="DR25" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="DS25" s="81" t="s">
+      <c r="DS25" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="DT25" s="81" t="s">
+      <c r="DT25" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="DU25" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="DV25" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="DW25" s="81" t="s">
+      <c r="DU25" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="DV25" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="DW25" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="DZ25" s="81" t="s">
+      <c r="DZ25" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="EA25" s="81" t="s">
+      <c r="EA25" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EB25" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EC25" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="ED25" s="81" t="s">
+      <c r="EB25" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EC25" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="ED25" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="EE25" s="81" t="s">
+      <c r="EE25" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="EF25" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EG25" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EH25" s="81" t="s">
+      <c r="EF25" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EG25" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EH25" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="EI25" s="81" t="s">
+      <c r="EI25" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="EJ25" s="81" t="s">
+      <c r="EJ25" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="EK25" s="81"/>
-      <c r="EL25" s="81" t="s">
+      <c r="EK25" s="80"/>
+      <c r="EL25" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="EM25" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="EN25" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="EO25" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EP25" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="EQ25" s="81" t="s">
+      <c r="EM25" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="EN25" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="EO25" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EP25" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="EQ25" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="ER25" s="81" t="s">
+      <c r="ER25" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="ES25" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="ET25" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="EU25" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="EV25" s="82" t="s">
+      <c r="ES25" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="ET25" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="EU25" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="EV25" s="81" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="A26" s="82" t="s">
+      <c r="A26" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="82" t="s">
+      <c r="B26" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="C26" s="82"/>
-      <c r="D26" s="82" t="s">
+      <c r="C26" s="81"/>
+      <c r="D26" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="82" t="s">
+      <c r="E26" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="F26" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H26" s="82"/>
-      <c r="I26" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J26" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N26" s="82"/>
-      <c r="O26" s="82" t="s">
+      <c r="F26" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="81"/>
+      <c r="I26" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" s="81"/>
+      <c r="O26" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="P26" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q26" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="R26" s="82"/>
-      <c r="S26" s="82"/>
-      <c r="T26" s="82"/>
-      <c r="U26" s="82"/>
-      <c r="V26" s="82"/>
-      <c r="W26" s="82"/>
-      <c r="X26" s="81" t="s">
+      <c r="P26" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q26" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="R26" s="81"/>
+      <c r="S26" s="81"/>
+      <c r="T26" s="81"/>
+      <c r="U26" s="81"/>
+      <c r="V26" s="81"/>
+      <c r="W26" s="81"/>
+      <c r="X26" s="80" t="s">
         <v>124</v>
       </c>
-      <c r="Y26" s="80" t="s">
+      <c r="Y26" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="A27" s="82" t="s">
+      <c r="A27" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="82" t="s">
+      <c r="B27" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="82"/>
-      <c r="D27" s="82" t="s">
+      <c r="C27" s="81"/>
+      <c r="D27" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="E27" s="82" t="s">
+      <c r="E27" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="F27" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G27" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H27" s="82"/>
-      <c r="I27" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J27" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N27" s="82"/>
-      <c r="O27" s="82" t="s">
+      <c r="F27" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J27" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N27" s="81"/>
+      <c r="O27" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="P27" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q27" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="R27" s="82"/>
-      <c r="S27" s="82"/>
-      <c r="T27" s="82"/>
-      <c r="U27" s="82"/>
-      <c r="V27" s="82"/>
-      <c r="W27" s="82"/>
-      <c r="X27" s="81" t="s">
+      <c r="P27" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q27" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="R27" s="81"/>
+      <c r="S27" s="81"/>
+      <c r="T27" s="81"/>
+      <c r="U27" s="81"/>
+      <c r="V27" s="81"/>
+      <c r="W27" s="81"/>
+      <c r="X27" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="Y27" s="80" t="s">
+      <c r="Y27" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="A28" s="82" t="s">
+      <c r="A28" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="82" t="s">
+      <c r="B28" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="82"/>
-      <c r="D28" s="82" t="s">
+      <c r="C28" s="81"/>
+      <c r="D28" s="81" t="s">
         <v>127</v>
       </c>
-      <c r="E28" s="82" t="s">
+      <c r="E28" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="F28" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G28" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H28" s="82"/>
-      <c r="I28" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J28" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N28" s="82"/>
-      <c r="O28" s="82" t="s">
+      <c r="F28" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G28" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J28" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N28" s="81"/>
+      <c r="O28" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="P28" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q28" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="R28" s="82"/>
-      <c r="S28" s="82"/>
-      <c r="T28" s="82"/>
-      <c r="U28" s="82"/>
-      <c r="V28" s="82"/>
-      <c r="W28" s="82"/>
-      <c r="X28" s="81" t="s">
+      <c r="P28" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q28" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="R28" s="81"/>
+      <c r="S28" s="81"/>
+      <c r="T28" s="81"/>
+      <c r="U28" s="81"/>
+      <c r="V28" s="81"/>
+      <c r="W28" s="81"/>
+      <c r="X28" s="80" t="s">
         <v>128</v>
       </c>
-      <c r="Y28" s="80" t="s">
+      <c r="Y28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="A29" s="82" t="s">
+      <c r="A29" s="81" t="s">
         <v>95</v>
       </c>
-      <c r="B29" s="82" t="s">
+      <c r="B29" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="C29" s="82"/>
-      <c r="D29" s="82" t="s">
+      <c r="C29" s="81"/>
+      <c r="D29" s="81" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="82" t="s">
+      <c r="E29" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="F29" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H29" s="82"/>
-      <c r="I29" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J29" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N29" s="82"/>
-      <c r="O29" s="82" t="s">
+      <c r="F29" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H29" s="81"/>
+      <c r="I29" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N29" s="81"/>
+      <c r="O29" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="P29" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q29" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="R29" s="82"/>
-      <c r="S29" s="82"/>
-      <c r="T29" s="82"/>
-      <c r="U29" s="82"/>
-      <c r="V29" s="82"/>
-      <c r="W29" s="82"/>
-      <c r="X29" s="81"/>
+      <c r="P29" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q29" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="R29" s="81"/>
+      <c r="S29" s="81"/>
+      <c r="T29" s="81"/>
+      <c r="U29" s="81"/>
+      <c r="V29" s="81"/>
+      <c r="W29" s="81"/>
+      <c r="X29" s="80"/>
     </row>
     <row r="30" spans="1:152" x14ac:dyDescent="0.25">
-      <c r="A30" s="82" t="s">
+      <c r="A30" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="B30" s="82" t="s">
+      <c r="B30" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="82"/>
-      <c r="D30" s="82" t="s">
+      <c r="C30" s="81"/>
+      <c r="D30" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="E30" s="82" t="s">
+      <c r="E30" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="F30" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G30" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H30" s="82"/>
-      <c r="I30" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="J30" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="N30" s="82"/>
-      <c r="O30" s="82" t="s">
+      <c r="F30" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="81"/>
+      <c r="I30" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J30" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="N30" s="81"/>
+      <c r="O30" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="P30" s="82" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q30" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="R30" s="82"/>
-      <c r="S30" s="82"/>
-      <c r="T30" s="82"/>
-      <c r="U30" s="82"/>
-      <c r="V30" s="82"/>
-      <c r="W30" s="82"/>
-      <c r="X30" s="81" t="s">
+      <c r="P30" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q30" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="R30" s="81"/>
+      <c r="S30" s="81"/>
+      <c r="T30" s="81"/>
+      <c r="U30" s="81"/>
+      <c r="V30" s="81"/>
+      <c r="W30" s="81"/>
+      <c r="X30" s="80" t="s">
         <v>129</v>
       </c>
-      <c r="Y30" s="80" t="s">
+      <c r="Y30" t="s">
         <v>130</v>
       </c>
     </row>
